--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Unicaja.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Unicaja.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2151</v>
+        <v>2464.440000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>2134.760000000001</v>
+        <v>2448.4</v>
       </c>
       <c r="D2" t="n">
-        <v>115.0012179355056</v>
+        <v>113.8702826335566</v>
       </c>
       <c r="E2" t="n">
-        <v>112.4716595776574</v>
+        <v>113.5843816369874</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5448613376835236</v>
+        <v>0.5397051830718022</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1396011396011396</v>
+        <v>0.1395874179524337</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3002944062806673</v>
+        <v>0.2969543147208122</v>
       </c>
       <c r="I2" t="n">
-        <v>0.245241979336596</v>
+        <v>0.2463147883975274</v>
       </c>
       <c r="J2" t="n">
-        <v>320</v>
+        <v>346</v>
       </c>
       <c r="K2" t="n">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="L2" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="M2" t="n">
-        <v>312</v>
+        <v>359</v>
       </c>
       <c r="N2" t="n">
-        <v>738</v>
+        <v>836</v>
       </c>
       <c r="O2" t="n">
-        <v>1016</v>
+        <v>1160</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5524741707449701</v>
+        <v>0.5515929624346172</v>
       </c>
       <c r="Q2" t="n">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="R2" t="n">
-        <v>336</v>
+        <v>380</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1827079934747145</v>
+        <v>0.1806942463147884</v>
       </c>
       <c r="T2" t="n">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="U2" t="n">
-        <v>276</v>
+        <v>328</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1500815660685155</v>
+        <v>0.1559676652401331</v>
       </c>
       <c r="W2" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="X2" t="n">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0989668297988037</v>
+        <v>0.09700427960057062</v>
       </c>
       <c r="Z2" t="n">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="AA2" t="n">
-        <v>654</v>
+        <v>757</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3556280587275693</v>
+        <v>0.359961959106039</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7263779527559056</v>
+        <v>0.7206896551724138</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.4789473684210526</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3695652173913043</v>
+        <v>0.3628048780487805</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.3970588235294117</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3547400611620795</v>
+        <v>0.3474240422721268</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.452755905511811</v>
+        <v>1.441379310344828</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.7391304347826086</v>
+        <v>0.725609756097561</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.083732057416268</v>
+        <v>1.073881373569199</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8556149732620321</v>
+        <v>0.8317307692307693</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.8562091503267973</v>
+        <v>0.8490028490028491</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.741573033707865</v>
+        <v>1.71875</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.513119533527697</v>
+        <v>1.491094147582697</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.361516034985423</v>
+        <v>5.351145038167939</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.87463556851312</v>
+        <v>6.842239185750636</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>76.82142857142858</v>
+        <v>77.01375000000003</v>
       </c>
       <c r="C3" t="n">
-        <v>76.2414285714286</v>
+        <v>76.5125</v>
       </c>
       <c r="D3" t="n">
-        <v>115.0012179355056</v>
+        <v>113.8702826335566</v>
       </c>
       <c r="E3" t="n">
-        <v>112.4716595776574</v>
+        <v>113.5843816369874</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5448613376835237</v>
+        <v>0.5397051830718022</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1396011396011396</v>
+        <v>0.1395874179524337</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3002944062806673</v>
+        <v>0.2969543147208122</v>
       </c>
       <c r="I3" t="n">
-        <v>0.245241979336596</v>
+        <v>0.2463147883975274</v>
       </c>
       <c r="J3" t="n">
-        <v>11.42857142857143</v>
+        <v>10.8125</v>
       </c>
       <c r="K3" t="n">
-        <v>9.357142857142858</v>
+        <v>9.3125</v>
       </c>
       <c r="L3" t="n">
-        <v>5.535714285714286</v>
+        <v>5.15625</v>
       </c>
       <c r="M3" t="n">
-        <v>11.14285714285714</v>
+        <v>11.21875</v>
       </c>
       <c r="N3" t="n">
-        <v>26.35714285714286</v>
+        <v>26.125</v>
       </c>
       <c r="O3" t="n">
-        <v>36.28571428571428</v>
+        <v>36.25</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5524741707449701</v>
+        <v>0.5515929624346172</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.714285714285714</v>
+        <v>5.6875</v>
       </c>
       <c r="R3" t="n">
-        <v>12</v>
+        <v>11.875</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1827079934747145</v>
+        <v>0.1806942463147884</v>
       </c>
       <c r="T3" t="n">
-        <v>3.642857142857143</v>
+        <v>3.71875</v>
       </c>
       <c r="U3" t="n">
-        <v>9.857142857142858</v>
+        <v>10.25</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1500815660685155</v>
+        <v>0.1559676652401331</v>
       </c>
       <c r="W3" t="n">
-        <v>2.5</v>
+        <v>2.53125</v>
       </c>
       <c r="X3" t="n">
-        <v>6.5</v>
+        <v>6.375</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0989668297988037</v>
+        <v>0.09700427960057062</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.285714285714286</v>
+        <v>8.21875</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.35714285714286</v>
+        <v>23.65625</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3556280587275693</v>
+        <v>0.359961959106039</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7263779527559056</v>
+        <v>0.7206896551724138</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.4789473684210526</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3695652173913043</v>
+        <v>0.3628048780487805</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.3970588235294117</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3547400611620795</v>
+        <v>0.3474240422721268</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.452755905511811</v>
+        <v>1.441379310344828</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.7391304347826086</v>
+        <v>0.725609756097561</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.083732057416268</v>
+        <v>1.073881373569199</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8556149732620321</v>
+        <v>0.8317307692307693</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.8562091503267975</v>
+        <v>0.8490028490028491</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.741573033707865</v>
+        <v>1.71875</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.513119533527697</v>
+        <v>1.491094147582697</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.361516034985423</v>
+        <v>5.351145038167939</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.874635568513121</v>
+        <v>6.842239185750636</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2118.52</v>
+        <v>2432.36</v>
       </c>
       <c r="C4" t="n">
-        <v>2134.760000000001</v>
+        <v>2448.4</v>
       </c>
       <c r="D4" t="n">
-        <v>112.4716595776574</v>
+        <v>113.5843816369874</v>
       </c>
       <c r="E4" t="n">
-        <v>115.0012179355056</v>
+        <v>113.8702826335566</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5532811559301626</v>
+        <v>0.5561594202898551</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1586412840612169</v>
+        <v>0.1535984876456601</v>
       </c>
       <c r="H4" t="n">
-        <v>0.263215859030837</v>
+        <v>0.2641148325358852</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3389524382901866</v>
+        <v>0.3271221532091098</v>
       </c>
       <c r="J4" t="n">
-        <v>274</v>
+        <v>316</v>
       </c>
       <c r="K4" t="n">
-        <v>238</v>
+        <v>278</v>
       </c>
       <c r="L4" t="n">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="M4" t="n">
-        <v>355</v>
+        <v>396</v>
       </c>
       <c r="N4" t="n">
-        <v>857</v>
+        <v>977</v>
       </c>
       <c r="O4" t="n">
-        <v>1114</v>
+        <v>1271</v>
       </c>
       <c r="P4" t="n">
-        <v>0.670680313064419</v>
+        <v>0.6578674948240165</v>
       </c>
       <c r="Q4" t="n">
-        <v>147</v>
+        <v>181</v>
       </c>
       <c r="R4" t="n">
-        <v>327</v>
+        <v>388</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1968693558097531</v>
+        <v>0.2008281573498965</v>
       </c>
       <c r="T4" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="U4" t="n">
-        <v>219</v>
+        <v>259</v>
       </c>
       <c r="V4" t="n">
-        <v>0.131848284166165</v>
+        <v>0.1340579710144928</v>
       </c>
       <c r="W4" t="n">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="X4" t="n">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.123419626730885</v>
+        <v>0.1185300207039337</v>
       </c>
       <c r="Z4" t="n">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="AA4" t="n">
-        <v>529</v>
+        <v>604</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3184828416616496</v>
+        <v>0.3126293995859213</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7692998204667864</v>
+        <v>0.7686860739575138</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4495412844036697</v>
+        <v>0.4664948453608248</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3607305936073059</v>
+        <v>0.3745173745173745</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4195121951219512</v>
+        <v>0.4323144104803494</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3402646502835538</v>
+        <v>0.3344370860927152</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.538599640933573</v>
+        <v>1.537372147915028</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.7214611872146118</v>
+        <v>0.749034749034749</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.087193460490463</v>
+        <v>1.084033613445378</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.7988338192419825</v>
+        <v>0.8040712468193384</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.99581589958159</v>
+        <v>1.007246376811594</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.825</v>
+        <v>1.75531914893617</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.235294117647059</v>
+        <v>1.302884615384615</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.441176470588236</v>
+        <v>4.644230769230769</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.676470588235294</v>
+        <v>5.947115384615385</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75.66142857142857</v>
+        <v>76.01125</v>
       </c>
       <c r="C5" t="n">
-        <v>76.2414285714286</v>
+        <v>76.5125</v>
       </c>
       <c r="D5" t="n">
-        <v>112.4716595776574</v>
+        <v>113.5843816369874</v>
       </c>
       <c r="E5" t="n">
-        <v>115.0012179355056</v>
+        <v>113.8702826335566</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5532811559301626</v>
+        <v>0.5561594202898551</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1586412840612169</v>
+        <v>0.1535984876456601</v>
       </c>
       <c r="H5" t="n">
-        <v>0.263215859030837</v>
+        <v>0.2641148325358852</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3389524382901867</v>
+        <v>0.3271221532091098</v>
       </c>
       <c r="J5" t="n">
-        <v>9.785714285714286</v>
+        <v>9.875</v>
       </c>
       <c r="K5" t="n">
-        <v>8.5</v>
+        <v>8.6875</v>
       </c>
       <c r="L5" t="n">
-        <v>5.214285714285714</v>
+        <v>5.15625</v>
       </c>
       <c r="M5" t="n">
-        <v>12.67857142857143</v>
+        <v>12.375</v>
       </c>
       <c r="N5" t="n">
-        <v>30.60714285714286</v>
+        <v>30.53125</v>
       </c>
       <c r="O5" t="n">
-        <v>39.78571428571428</v>
+        <v>39.71875</v>
       </c>
       <c r="P5" t="n">
-        <v>0.670680313064419</v>
+        <v>0.6578674948240165</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.25</v>
+        <v>5.65625</v>
       </c>
       <c r="R5" t="n">
-        <v>11.67857142857143</v>
+        <v>12.125</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1968693558097532</v>
+        <v>0.2008281573498965</v>
       </c>
       <c r="T5" t="n">
-        <v>2.821428571428572</v>
+        <v>3.03125</v>
       </c>
       <c r="U5" t="n">
-        <v>7.821428571428571</v>
+        <v>8.09375</v>
       </c>
       <c r="V5" t="n">
-        <v>0.131848284166165</v>
+        <v>0.1340579710144928</v>
       </c>
       <c r="W5" t="n">
-        <v>3.071428571428572</v>
+        <v>3.09375</v>
       </c>
       <c r="X5" t="n">
-        <v>7.321428571428571</v>
+        <v>7.15625</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.123419626730885</v>
+        <v>0.1185300207039337</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.428571428571429</v>
+        <v>6.3125</v>
       </c>
       <c r="AA5" t="n">
-        <v>18.89285714285714</v>
+        <v>18.875</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3184828416616496</v>
+        <v>0.3126293995859213</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7692998204667864</v>
+        <v>0.7686860739575138</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4495412844036697</v>
+        <v>0.4664948453608248</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.360730593607306</v>
+        <v>0.3745173745173745</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4195121951219513</v>
+        <v>0.4323144104803494</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3402646502835539</v>
+        <v>0.3344370860927152</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.538599640933573</v>
+        <v>1.537372147915028</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.7214611872146119</v>
+        <v>0.749034749034749</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.087193460490463</v>
+        <v>1.084033613445378</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.7988338192419826</v>
+        <v>0.8040712468193384</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.9958158995815899</v>
+        <v>1.007246376811594</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.825</v>
+        <v>1.75531914893617</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.235294117647059</v>
+        <v>1.302884615384615</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.441176470588235</v>
+        <v>4.644230769230769</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.676470588235293</v>
+        <v>5.947115384615385</v>
       </c>
     </row>
     <row r="7">
@@ -1419,67 +1419,67 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="D8" t="n">
+        <v>43</v>
+      </c>
+      <c r="E8" t="n">
+        <v>79</v>
+      </c>
+      <c r="F8" t="n">
+        <v>14</v>
+      </c>
+      <c r="G8" t="n">
         <v>37</v>
       </c>
-      <c r="E8" t="n">
-        <v>69</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
+        <v>32</v>
+      </c>
+      <c r="I8" t="n">
+        <v>46</v>
+      </c>
+      <c r="J8" t="n">
         <v>12</v>
       </c>
-      <c r="G8" t="n">
+      <c r="K8" t="n">
+        <v>85</v>
+      </c>
+      <c r="L8" t="n">
+        <v>44</v>
+      </c>
+      <c r="M8" t="n">
+        <v>18</v>
+      </c>
+      <c r="N8" t="n">
+        <v>12</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+      <c r="R8" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" t="n">
         <v>32</v>
       </c>
-      <c r="H8" t="n">
-        <v>31</v>
-      </c>
-      <c r="I8" t="n">
-        <v>44</v>
-      </c>
-      <c r="J8" t="n">
-        <v>11</v>
-      </c>
-      <c r="K8" t="n">
-        <v>80</v>
-      </c>
-      <c r="L8" t="n">
-        <v>43</v>
-      </c>
-      <c r="M8" t="n">
-        <v>16</v>
-      </c>
-      <c r="N8" t="n">
-        <v>9</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>17</v>
-      </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
+        <v>239</v>
+      </c>
+      <c r="U8" t="n">
         <v>30</v>
       </c>
-      <c r="S8" t="n">
-        <v>30</v>
-      </c>
-      <c r="T8" t="n">
-        <v>218</v>
-      </c>
-      <c r="U8" t="n">
-        <v>25</v>
-      </c>
       <c r="V8" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="W8" t="n">
         <v>8</v>
@@ -1488,87 +1488,87 @@
         <v>5</v>
       </c>
       <c r="Y8" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="Z8" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.659</v>
+        <v>0.663</v>
       </c>
       <c r="AB8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AC8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.529</v>
+        <v>0.524</v>
       </c>
       <c r="AE8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF8" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.357</v>
+        <v>0.389</v>
       </c>
       <c r="AH8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.357</v>
+        <v>0.4</v>
       </c>
       <c r="AK8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL8" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.389</v>
+        <v>0.364</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>336:07</t>
+          <t>370:51</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>137.36</v>
+        <v>154.24</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.545</v>
+        <v>0.552</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.586</v>
+        <v>0.587</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.026</v>
+        <v>1.037</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.124</v>
+        <v>0.117</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.307</v>
+        <v>0.276</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.647</v>
+        <v>0.667</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.187</v>
+        <v>0.191</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.141</v>
+        <v>0.129</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.295</v>
+        <v>0.283</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="9">
@@ -1578,156 +1578,156 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
+        <v>131</v>
+      </c>
+      <c r="D9" t="n">
+        <v>29</v>
+      </c>
+      <c r="E9" t="n">
+        <v>54</v>
+      </c>
+      <c r="F9" t="n">
+        <v>22</v>
+      </c>
+      <c r="G9" t="n">
+        <v>60</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>17</v>
+      </c>
+      <c r="J9" t="n">
+        <v>23</v>
+      </c>
+      <c r="K9" t="n">
+        <v>15</v>
+      </c>
+      <c r="L9" t="n">
+        <v>14</v>
+      </c>
+      <c r="M9" t="n">
+        <v>13</v>
+      </c>
+      <c r="N9" t="n">
+        <v>14</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>16</v>
+      </c>
+      <c r="R9" t="n">
+        <v>40</v>
+      </c>
+      <c r="S9" t="n">
+        <v>18</v>
+      </c>
+      <c r="T9" t="n">
         <v>99</v>
       </c>
-      <c r="D9" t="n">
-        <v>23</v>
-      </c>
-      <c r="E9" t="n">
-        <v>42</v>
-      </c>
-      <c r="F9" t="n">
-        <v>16</v>
-      </c>
-      <c r="G9" t="n">
-        <v>49</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5</v>
-      </c>
-      <c r="I9" t="n">
-        <v>11</v>
-      </c>
-      <c r="J9" t="n">
-        <v>18</v>
-      </c>
-      <c r="K9" t="n">
-        <v>10</v>
-      </c>
-      <c r="L9" t="n">
-        <v>8</v>
-      </c>
-      <c r="M9" t="n">
-        <v>11</v>
-      </c>
-      <c r="N9" t="n">
-        <v>10</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>12</v>
-      </c>
-      <c r="R9" t="n">
-        <v>31</v>
-      </c>
-      <c r="S9" t="n">
-        <v>12</v>
-      </c>
-      <c r="T9" t="n">
-        <v>67</v>
-      </c>
       <c r="U9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="V9" t="n">
         <v>7</v>
       </c>
       <c r="W9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y9" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC9" t="n">
         <v>18</v>
       </c>
-      <c r="Z9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.643</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>15</v>
-      </c>
       <c r="AD9" t="n">
-        <v>0.467</v>
+        <v>0.5</v>
       </c>
       <c r="AE9" t="n">
         <v>3</v>
       </c>
       <c r="AF9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.3</v>
+        <v>0.231</v>
       </c>
       <c r="AH9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AI9" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.48</v>
+        <v>0.467</v>
       </c>
       <c r="AK9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AL9" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.167</v>
+        <v>0.267</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>256:09</t>
+          <t>322:05</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>107.84</v>
+        <v>137.48</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.516</v>
+        <v>0.544</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.516</v>
+        <v>0.539</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.918</v>
+        <v>0.953</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.111</v>
+        <v>0.116</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.055</v>
+        <v>0.061</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.5</v>
+        <v>1.438</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.193</v>
+        <v>0.196</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.034</v>
+        <v>0.047</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.048</v>
+        <v>0.057</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.022</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="10">
@@ -1737,67 +1737,67 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C10" t="n">
-        <v>297</v>
+        <v>331</v>
       </c>
       <c r="D10" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E10" t="n">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H10" t="n">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="I10" t="n">
-        <v>136</v>
+        <v>163</v>
       </c>
       <c r="J10" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K10" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L10" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M10" t="n">
         <v>11</v>
       </c>
       <c r="N10" t="n">
+        <v>35</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>41</v>
+      </c>
+      <c r="R10" t="n">
+        <v>95</v>
+      </c>
+      <c r="S10" t="n">
+        <v>132</v>
+      </c>
+      <c r="T10" t="n">
+        <v>391</v>
+      </c>
+      <c r="U10" t="n">
         <v>32</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>39</v>
-      </c>
-      <c r="R10" t="n">
-        <v>81</v>
-      </c>
-      <c r="S10" t="n">
-        <v>112</v>
-      </c>
-      <c r="T10" t="n">
-        <v>351</v>
-      </c>
-      <c r="U10" t="n">
-        <v>30</v>
-      </c>
       <c r="V10" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="W10" t="n">
         <v>12</v>
@@ -1806,31 +1806,31 @@
         <v>9</v>
       </c>
       <c r="Y10" t="n">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="Z10" t="n">
-        <v>219</v>
+        <v>252</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.717</v>
+        <v>0.706</v>
       </c>
       <c r="AB10" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="AC10" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.54</v>
+        <v>0.554</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -1845,48 +1845,48 @@
         <v>5</v>
       </c>
       <c r="AL10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.385</v>
+        <v>0.333</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>561:57</t>
+          <t>640:40</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>258.84</v>
+        <v>288.72</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.647</v>
+        <v>0.639</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.675</v>
+        <v>0.668</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.147</v>
+        <v>1.146</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.151</v>
+        <v>0.142</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.602</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.769</v>
+        <v>0.805</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.211</v>
+        <v>0.206</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.067</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.132</v>
+        <v>0.127</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.04</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="11">
@@ -1896,67 +1896,67 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>237</v>
+        <v>282</v>
       </c>
       <c r="D11" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E11" t="n">
+        <v>111</v>
+      </c>
+      <c r="F11" t="n">
+        <v>39</v>
+      </c>
+      <c r="G11" t="n">
         <v>91</v>
       </c>
-      <c r="F11" t="n">
-        <v>31</v>
-      </c>
-      <c r="G11" t="n">
-        <v>75</v>
-      </c>
       <c r="H11" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="I11" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="J11" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="L11" t="n">
+        <v>23</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20</v>
+      </c>
+      <c r="N11" t="n">
+        <v>9</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>39</v>
+      </c>
+      <c r="R11" t="n">
+        <v>74</v>
+      </c>
+      <c r="S11" t="n">
+        <v>56</v>
+      </c>
+      <c r="T11" t="n">
+        <v>274</v>
+      </c>
+      <c r="U11" t="n">
         <v>18</v>
       </c>
-      <c r="M11" t="n">
+      <c r="V11" t="n">
         <v>18</v>
-      </c>
-      <c r="N11" t="n">
-        <v>8</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>33</v>
-      </c>
-      <c r="R11" t="n">
-        <v>65</v>
-      </c>
-      <c r="S11" t="n">
-        <v>48</v>
-      </c>
-      <c r="T11" t="n">
-        <v>238</v>
-      </c>
-      <c r="U11" t="n">
-        <v>14</v>
-      </c>
-      <c r="V11" t="n">
-        <v>15</v>
       </c>
       <c r="W11" t="n">
         <v>22</v>
@@ -1965,87 +1965,87 @@
         <v>12</v>
       </c>
       <c r="Y11" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="Z11" t="n">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.79</v>
+        <v>0.757</v>
       </c>
       <c r="AB11" t="n">
         <v>15</v>
       </c>
       <c r="AC11" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.484</v>
+        <v>0.417</v>
       </c>
       <c r="AE11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="AH11" t="n">
         <v>11</v>
       </c>
-      <c r="AF11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.478</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>7</v>
-      </c>
       <c r="AI11" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.368</v>
+        <v>0.44</v>
       </c>
       <c r="AK11" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AL11" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.429</v>
+        <v>0.424</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>507:47</t>
+          <t>617:16</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>218.36</v>
+        <v>266.08</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.605</v>
+        <v>0.587</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.639</v>
+        <v>0.621</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.085</v>
+        <v>1.06</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.151</v>
+        <v>0.147</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.217</v>
+        <v>0.223</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.515</v>
+        <v>0.513</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.197</v>
+        <v>0.198</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.039</v>
+        <v>0.041</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.193</v>
+        <v>0.184</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="12">
@@ -2055,67 +2055,67 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="D12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="H12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K12" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="L12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M12" t="n">
+        <v>26</v>
+      </c>
+      <c r="N12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>22</v>
+      </c>
+      <c r="R12" t="n">
+        <v>79</v>
+      </c>
+      <c r="S12" t="n">
         <v>24</v>
-      </c>
-      <c r="N12" t="n">
-        <v>10</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>19</v>
-      </c>
-      <c r="R12" t="n">
-        <v>64</v>
-      </c>
-      <c r="S12" t="n">
-        <v>23</v>
       </c>
       <c r="T12" t="n">
         <v>148</v>
       </c>
       <c r="U12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="V12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="W12" t="n">
         <v>7</v>
@@ -2124,87 +2124,87 @@
         <v>4</v>
       </c>
       <c r="Y12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Z12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.667</v>
       </c>
       <c r="AB12" t="n">
         <v>4</v>
       </c>
       <c r="AC12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.235</v>
+        <v>0.211</v>
       </c>
       <c r="AE12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.462</v>
+        <v>0.467</v>
       </c>
       <c r="AH12" t="n">
         <v>4</v>
       </c>
       <c r="AI12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.19</v>
+        <v>0.174</v>
       </c>
       <c r="AK12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AL12" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.373</v>
+        <v>0.356</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>479:12</t>
+          <t>556:36</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>183.88</v>
+        <v>212.76</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.464</v>
+        <v>0.449</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.494</v>
+        <v>0.477</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.886</v>
+        <v>0.855</v>
       </c>
       <c r="AS12" t="n">
         <v>0.103</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.137</v>
+        <v>0.124</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.947</v>
+        <v>2.636</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.176</v>
+        <v>0.175</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.053</v>
+        <v>0.051</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.093</v>
+        <v>0.098</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="13">
@@ -2214,67 +2214,67 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="D13" t="n">
+        <v>22</v>
+      </c>
+      <c r="E13" t="n">
+        <v>39</v>
+      </c>
+      <c r="F13" t="n">
+        <v>21</v>
+      </c>
+      <c r="G13" t="n">
+        <v>76</v>
+      </c>
+      <c r="H13" t="n">
+        <v>23</v>
+      </c>
+      <c r="I13" t="n">
+        <v>36</v>
+      </c>
+      <c r="J13" t="n">
         <v>18</v>
       </c>
-      <c r="E13" t="n">
-        <v>33</v>
-      </c>
-      <c r="F13" t="n">
-        <v>18</v>
-      </c>
-      <c r="G13" t="n">
-        <v>62</v>
-      </c>
-      <c r="H13" t="n">
+      <c r="K13" t="n">
+        <v>63</v>
+      </c>
+      <c r="L13" t="n">
+        <v>24</v>
+      </c>
+      <c r="M13" t="n">
         <v>17</v>
       </c>
-      <c r="I13" t="n">
-        <v>28</v>
-      </c>
-      <c r="J13" t="n">
-        <v>16</v>
-      </c>
-      <c r="K13" t="n">
-        <v>40</v>
-      </c>
-      <c r="L13" t="n">
-        <v>19</v>
-      </c>
-      <c r="M13" t="n">
-        <v>14</v>
-      </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R13" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="S13" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="T13" t="n">
-        <v>116</v>
+        <v>159</v>
       </c>
       <c r="U13" t="n">
         <v>9</v>
       </c>
       <c r="V13" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="W13" t="n">
         <v>9</v>
@@ -2283,84 +2283,84 @@
         <v>4</v>
       </c>
       <c r="Y13" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>59</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI13" t="n">
         <v>31</v>
       </c>
-      <c r="Z13" t="n">
-        <v>47</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>27</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>0.259</v>
+        <v>0.258</v>
       </c>
       <c r="AK13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AL13" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.314</v>
+        <v>0.289</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>416:15</t>
+          <t>496:18</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>117.32</v>
+        <v>142.84</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.474</v>
+        <v>0.465</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.499</v>
+        <v>0.497</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.912</v>
+        <v>0.91</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.179</v>
+        <v>0.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.129</v>
+        <v>0.132</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.05</v>
+        <v>0.053</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.119</v>
+        <v>0.157</v>
       </c>
       <c r="AY13" t="n">
         <v>0.02</v>
@@ -2373,40 +2373,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C14" t="n">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E14" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F14" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G14" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="H14" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="I14" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J14" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="K14" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="L14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M14" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
@@ -2415,22 +2415,22 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Q14" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="R14" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="T14" t="n">
-        <v>237</v>
+        <v>286</v>
       </c>
       <c r="U14" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="V14" t="n">
         <v>14</v>
@@ -2442,87 +2442,87 @@
         <v>2</v>
       </c>
       <c r="Y14" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="Z14" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.857</v>
+        <v>0.843</v>
       </c>
       <c r="AB14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.625</v>
+        <v>0.636</v>
       </c>
       <c r="AE14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.476</v>
+        <v>0.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AI14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.75</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AK14" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AL14" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.333</v>
+        <v>0.323</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>505:47</t>
+          <t>591:08</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>120.84</v>
+        <v>149.8</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.569</v>
+        <v>0.583</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.633</v>
+        <v>0.643</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.15</v>
+        <v>1.148</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.091</v>
+        <v>0.107</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.34</v>
+        <v>0.342</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.909</v>
+        <v>5.562</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.109</v>
+        <v>0.116</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.037</v>
+        <v>0.033</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.11</v>
+        <v>0.113</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.094</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="15">
@@ -2532,34 +2532,34 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
+        <v>21</v>
+      </c>
+      <c r="F15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G15" t="n">
+        <v>26</v>
+      </c>
+      <c r="H15" t="n">
+        <v>15</v>
+      </c>
+      <c r="I15" t="n">
         <v>17</v>
       </c>
-      <c r="F15" t="n">
+      <c r="J15" t="n">
+        <v>12</v>
+      </c>
+      <c r="K15" t="n">
         <v>11</v>
-      </c>
-      <c r="G15" t="n">
-        <v>20</v>
-      </c>
-      <c r="H15" t="n">
-        <v>8</v>
-      </c>
-      <c r="I15" t="n">
-        <v>8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>10</v>
-      </c>
-      <c r="K15" t="n">
-        <v>6</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2568,25 +2568,25 @@
         <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="T15" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
         <v>8</v>
@@ -2595,19 +2595,19 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y15" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Z15" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.909</v>
+        <v>0.85</v>
       </c>
       <c r="AB15" t="n">
         <v>2</v>
@@ -2619,13 +2619,13 @@
         <v>1</v>
       </c>
       <c r="AE15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AF15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.5</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AH15" t="n">
         <v>2</v>
@@ -2637,51 +2637,51 @@
         <v>0.4</v>
       </c>
       <c r="AK15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL15" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.6</v>
+        <v>0.476</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>108:48</t>
+          <t>144:38</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>41.52</v>
+        <v>56.48</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.716</v>
+        <v>0.66</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.753</v>
+        <v>0.707</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.469</v>
+        <v>1.363</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.024</v>
+        <v>0.035</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.216</v>
+        <v>0.319</v>
       </c>
       <c r="AU15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.175</v>
+        <v>0.179</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.068</v>
+        <v>0.094</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="16">
@@ -2831,7 +2831,7 @@
         <v>1</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.216</v>
+        <v>0.217</v>
       </c>
       <c r="AW16" t="n">
         <v>0.02</v>
@@ -2840,7 +2840,7 @@
         <v>0.023</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="17">
@@ -2990,7 +2990,7 @@
         <v>0.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.224</v>
+        <v>0.225</v>
       </c>
       <c r="AW17" t="n">
         <v>0.038</v>
@@ -2999,7 +2999,7 @@
         <v>0.128</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="18">
@@ -3009,40 +3009,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C18" t="n">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="D18" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E18" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G18" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H18" t="n">
         <v>20</v>
       </c>
       <c r="I18" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J18" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K18" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="L18" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N18" t="n">
         <v>14</v>
@@ -3051,25 +3051,25 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R18" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="S18" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="T18" t="n">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="U18" t="n">
         <v>17</v>
       </c>
       <c r="V18" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="W18" t="n">
         <v>5</v>
@@ -3081,19 +3081,19 @@
         <v>48</v>
       </c>
       <c r="Z18" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.615</v>
+        <v>0.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AC18" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AE18" t="n">
         <v>3</v>
@@ -3108,57 +3108,57 @@
         <v>3</v>
       </c>
       <c r="AI18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="AK18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL18" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.375</v>
+        <v>0.372</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>400:07</t>
+          <t>428:05</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>179.36</v>
+        <v>189.24</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.555</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.55</v>
+        <v>0.554</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.959</v>
+        <v>0.967</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.128</v>
+        <v>0.127</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.146</v>
+        <v>0.138</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.087</v>
+        <v>1.167</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.205</v>
+        <v>0.203</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.11</v>
+        <v>0.107</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.245</v>
+        <v>0.239</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.032</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="19">
@@ -3168,40 +3168,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E19" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I19" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="J19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K19" t="n">
+        <v>21</v>
+      </c>
+      <c r="L19" t="n">
         <v>16</v>
       </c>
-      <c r="L19" t="n">
-        <v>14</v>
-      </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N19" t="n">
         <v>5</v>
@@ -3210,49 +3210,49 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R19" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="S19" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="T19" t="n">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="U19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="Z19" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.709</v>
+        <v>0.701</v>
       </c>
       <c r="AB19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC19" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.333</v>
+        <v>0.421</v>
       </c>
       <c r="AE19" t="n">
         <v>14</v>
@@ -3276,48 +3276,48 @@
         <v>1</v>
       </c>
       <c r="AL19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>196:06</t>
+          <t>232:56</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>87.72</v>
+        <v>102.24</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.508</v>
+        <v>0.507</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.578</v>
+        <v>0.58</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.037</v>
+        <v>1.047</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.103</v>
+        <v>0.098</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.452</v>
+        <v>0.472</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.222</v>
+        <v>1.3</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.205</v>
+        <v>0.201</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.079</v>
+        <v>0.075</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.101</v>
+        <v>0.111</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="20">
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -3470,7 +3470,7 @@
         <v>0.114</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.275</v>
+        <v>0.272</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
@@ -3486,37 +3486,37 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="n">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="D21" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E21" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F21" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G21" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H21" t="n">
         <v>72</v>
       </c>
       <c r="I21" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J21" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K21" t="n">
         <v>43</v>
       </c>
       <c r="L21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M21" t="n">
         <v>17</v>
@@ -3534,16 +3534,16 @@
         <v>40</v>
       </c>
       <c r="R21" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="S21" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T21" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="U21" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="V21" t="n">
         <v>18</v>
@@ -3555,31 +3555,31 @@
         <v>14</v>
       </c>
       <c r="Y21" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Z21" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.857</v>
+        <v>0.851</v>
       </c>
       <c r="AB21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC21" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.545</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AE21" t="n">
         <v>10</v>
       </c>
       <c r="AF21" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.37</v>
+        <v>0.345</v>
       </c>
       <c r="AH21" t="n">
         <v>9</v>
@@ -3591,51 +3591,51 @@
         <v>0.529</v>
       </c>
       <c r="AK21" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AL21" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AM21" t="n">
         <v>0.33</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>475:12</t>
+          <t>485:11</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>284.76</v>
+        <v>292.2</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.548</v>
+        <v>0.546</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.617</v>
+        <v>0.613</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.061</v>
+        <v>1.057</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.14</v>
+        <v>0.137</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.343</v>
+        <v>0.332</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.925</v>
+        <v>1.95</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.274</v>
+        <v>0.276</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.112</v>
+        <v>0.109</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.102</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="22">
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C22" t="n">
         <v>133</v>
@@ -3654,13 +3654,13 @@
         <v>20</v>
       </c>
       <c r="E22" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F22" t="n">
         <v>28</v>
       </c>
       <c r="G22" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H22" t="n">
         <v>9</v>
@@ -3672,34 +3672,34 @@
         <v>21</v>
       </c>
       <c r="K22" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q22" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="R22" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S22" t="n">
         <v>23</v>
       </c>
       <c r="T22" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="U22" t="n">
         <v>10</v>
@@ -3726,10 +3726,10 @@
         <v>8</v>
       </c>
       <c r="AC22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.571</v>
+        <v>0.5</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -3753,48 +3753,48 @@
         <v>21</v>
       </c>
       <c r="AL22" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.396</v>
+        <v>0.375</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>317:58</t>
+          <t>333:13</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>142.04</v>
+        <v>150.04</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.521</v>
+        <v>0.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.528</v>
+        <v>0.507</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.886</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.113</v>
+        <v>0.127</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.076</v>
+        <v>0.073</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.312</v>
+        <v>1.105</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.205</v>
+        <v>0.206</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.083</v>
+        <v>0.082</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.129</v>
+        <v>0.126</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.026</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="23">
@@ -3804,100 +3804,100 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C23" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E23" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>13</v>
+      </c>
+      <c r="K23" t="n">
+        <v>15</v>
+      </c>
+      <c r="L23" t="n">
+        <v>8</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>2</v>
       </c>
-      <c r="I23" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>7</v>
-      </c>
-      <c r="K23" t="n">
-        <v>10</v>
-      </c>
-      <c r="L23" t="n">
-        <v>4</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="R23" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T23" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="U23" t="n">
         <v>3</v>
       </c>
       <c r="V23" t="n">
+        <v>8</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="AB23" t="n">
         <v>6</v>
       </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>4</v>
-      </c>
       <c r="AC23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="AE23" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AF23" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
@@ -3912,48 +3912,48 @@
         <v>2</v>
       </c>
       <c r="AL23" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.286</v>
+        <v>0.154</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>78:37</t>
+          <t>145:31</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>32.88</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.5</v>
+        <v>0.418</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.519</v>
+        <v>0.432</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.912</v>
+        <v>0.702</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.122</v>
+        <v>0.186</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.055</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.191</v>
+        <v>0.22</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.056</v>
+        <v>0.06</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.158</v>
+        <v>0.127</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.008</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="24">
@@ -3963,61 +3963,61 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C24" t="n">
-        <v>298</v>
+        <v>357</v>
       </c>
       <c r="D24" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E24" t="n">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="F24" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G24" t="n">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="H24" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I24" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="J24" t="n">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="K24" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M24" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="N24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="Q24" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="R24" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="S24" t="n">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="T24" t="n">
-        <v>357</v>
+        <v>434</v>
       </c>
       <c r="U24" t="n">
         <v>44</v>
@@ -4026,37 +4026,37 @@
         <v>24</v>
       </c>
       <c r="W24" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="X24" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>92</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>113</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>45</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="AE24" t="n">
         <v>16</v>
       </c>
-      <c r="Y24" t="n">
-        <v>74</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>93</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.796</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>41</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0.317</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>15</v>
-      </c>
       <c r="AF24" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.341</v>
+        <v>0.308</v>
       </c>
       <c r="AH24" t="n">
         <v>3</v>
@@ -4068,51 +4068,51 @@
         <v>0.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="AL24" t="n">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.395</v>
+        <v>0.404</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>610:49</t>
+          <t>713:28</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>301.6</v>
+        <v>357.88</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.532</v>
+        <v>0.538</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.57</v>
+        <v>0.578</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.988</v>
+        <v>0.998</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.133</v>
+        <v>0.137</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.215</v>
+        <v>0.222</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.226</v>
+        <v>0.23</v>
       </c>
       <c r="AW24" t="n">
         <v>0.018</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.083</v>
+        <v>0.081</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.162</v>
+        <v>0.173</v>
       </c>
     </row>
     <row r="25">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -4308,10 +4308,10 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="L26" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -4323,7 +4323,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4436,157 +4436,157 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>2788</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>619</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1142</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>961</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>518</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>726</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>586</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>769</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>393</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>359</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>766</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>717</v>
       </c>
       <c r="T27" t="n">
-        <v>46</v>
+        <v>3099</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>298</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>836</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1160</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>0.721</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>0.479</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>0.363</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>0.397</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>757</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>0.347</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>6450:00</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>31</v>
+        <v>2815.44</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>0.575</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>0.246</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>1.491</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>0.147</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -4595,157 +4595,157 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C28" t="n">
-        <v>2455</v>
+        <v>2781</v>
       </c>
       <c r="D28" t="n">
-        <v>549</v>
+        <v>623</v>
       </c>
       <c r="E28" t="n">
-        <v>1003</v>
+        <v>1099</v>
       </c>
       <c r="F28" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G28" t="n">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="H28" t="n">
-        <v>451</v>
+        <v>632</v>
       </c>
       <c r="I28" t="n">
-        <v>625</v>
+        <v>819</v>
       </c>
       <c r="J28" t="n">
-        <v>519</v>
+        <v>542</v>
       </c>
       <c r="K28" t="n">
-        <v>669</v>
+        <v>831</v>
       </c>
       <c r="L28" t="n">
-        <v>306</v>
+        <v>276</v>
       </c>
       <c r="M28" t="n">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="N28" t="n">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>343</v>
+        <v>416</v>
       </c>
       <c r="Q28" t="n">
-        <v>312</v>
+        <v>396</v>
       </c>
       <c r="R28" t="n">
-        <v>675</v>
+        <v>722</v>
       </c>
       <c r="S28" t="n">
-        <v>622</v>
+        <v>764</v>
       </c>
       <c r="T28" t="n">
-        <v>2736</v>
+        <v>3212</v>
       </c>
       <c r="U28" t="n">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="V28" t="n">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="W28" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="X28" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="Y28" t="n">
-        <v>738</v>
+        <v>977</v>
       </c>
       <c r="Z28" t="n">
-        <v>1016</v>
+        <v>1271</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.726</v>
+        <v>0.769</v>
       </c>
       <c r="AB28" t="n">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="AC28" t="n">
-        <v>336</v>
+        <v>388</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.476</v>
+        <v>0.466</v>
       </c>
       <c r="AE28" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="AF28" t="n">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.37</v>
+        <v>0.375</v>
       </c>
       <c r="AH28" t="n">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="AI28" t="n">
-        <v>182</v>
+        <v>229</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.385</v>
+        <v>0.432</v>
       </c>
       <c r="AK28" t="n">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="AL28" t="n">
-        <v>654</v>
+        <v>604</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.355</v>
+        <v>0.334</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>5625:00</t>
+          <t>6450:00</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>2457</v>
+        <v>2708.36</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.545</v>
+        <v>0.556</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.581</v>
+        <v>0.607</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.999</v>
+        <v>1.027</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.14</v>
+        <v>0.154</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.245</v>
+        <v>0.327</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.513</v>
+        <v>1.303</v>
       </c>
       <c r="AV28" t="n">
         <v>0.2</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.06</v>
+        <v>0.053</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.147</v>
+        <v>0.141</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
@@ -4754,1532 +4754,1532 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>28</v>
-      </c>
-      <c r="C29" t="n">
-        <v>2401</v>
-      </c>
-      <c r="D29" t="n">
-        <v>520</v>
-      </c>
-      <c r="E29" t="n">
-        <v>927</v>
-      </c>
-      <c r="F29" t="n">
-        <v>266</v>
-      </c>
-      <c r="G29" t="n">
-        <v>734</v>
-      </c>
-      <c r="H29" t="n">
-        <v>563</v>
-      </c>
-      <c r="I29" t="n">
-        <v>733</v>
-      </c>
-      <c r="J29" t="n">
-        <v>462</v>
-      </c>
-      <c r="K29" t="n">
-        <v>713</v>
-      </c>
-      <c r="L29" t="n">
-        <v>239</v>
-      </c>
-      <c r="M29" t="n">
-        <v>168</v>
-      </c>
-      <c r="N29" t="n">
-        <v>136</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>374</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>355</v>
-      </c>
-      <c r="R29" t="n">
-        <v>627</v>
-      </c>
-      <c r="S29" t="n">
-        <v>674</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2747</v>
-      </c>
-      <c r="U29" t="n">
-        <v>274</v>
-      </c>
-      <c r="V29" t="n">
-        <v>238</v>
-      </c>
-      <c r="W29" t="n">
-        <v>146</v>
-      </c>
-      <c r="X29" t="n">
-        <v>80</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>857</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1114</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0.769</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>147</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>327</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>79</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>219</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>86</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>205</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>180</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>529</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>5625:00</t>
-        </is>
-      </c>
-      <c r="AO29" t="n">
-        <v>2357.52</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0.553</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.018</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0.339</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>1.235</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
-      <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="inlineStr"/>
-      <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="inlineStr"/>
-      <c r="AR30" t="inlineStr"/>
-      <c r="AS30" t="inlineStr"/>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AU30" t="inlineStr"/>
-      <c r="AV30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr"/>
-      <c r="AX30" t="inlineStr"/>
-      <c r="AY30" t="inlineStr"/>
+          <t>#0 T. PÉREZ (Per Game)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>22</v>
+      </c>
+      <c r="C30" t="n">
+        <v>7.273</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.955</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3.591</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.682</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.455</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.091</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.864</v>
+      </c>
+      <c r="L30" t="n">
+        <v>2</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.455</v>
+      </c>
+      <c r="T30" t="n">
+        <v>239</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.364</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>2.591</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.909</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AO30" t="n">
+        <v>7.011</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#0 T. PÉREZ (Per Game)</t>
+          <t>#1 C. AUDIGE (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C31" t="n">
-        <v>7.05</v>
+        <v>5.696</v>
       </c>
       <c r="D31" t="n">
-        <v>1.85</v>
+        <v>1.261</v>
       </c>
       <c r="E31" t="n">
-        <v>3.45</v>
+        <v>2.348</v>
       </c>
       <c r="F31" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.609</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.739</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="T31" t="n">
+        <v>99</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.739</v>
+      </c>
+      <c r="AA31" t="n">
         <v>0.6</v>
       </c>
-      <c r="G31" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="I31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="K31" t="n">
-        <v>4</v>
-      </c>
-      <c r="L31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T31" t="n">
-        <v>218</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0.659</v>
-      </c>
       <c r="AB31" t="n">
-        <v>0.45</v>
+        <v>0.391</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.85</v>
+        <v>0.783</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.529</v>
+        <v>0.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.25</v>
+        <v>0.13</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.7</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.357</v>
+        <v>0.231</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.25</v>
+        <v>0.609</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.7</v>
+        <v>1.304</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.357</v>
+        <v>0.467</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.35</v>
+        <v>0.348</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.9</v>
+        <v>1.304</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.389</v>
+        <v>0.267</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>6.868</v>
+        <v>5.977</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.545</v>
+        <v>0.544</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.586</v>
+        <v>0.539</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.026</v>
+        <v>0.953</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.124</v>
+        <v>0.116</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.307</v>
+        <v>0.061</v>
       </c>
       <c r="AU31" t="n">
-        <v>0.647</v>
+        <v>1.438</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.187</v>
+        <v>0.196</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.141</v>
+        <v>0.047</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.295</v>
+        <v>0.057</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.02</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#1 C. AUDIGE (Per Game)</t>
+          <t>#2 O. BALCEROWSKI (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C32" t="n">
-        <v>5.211</v>
+        <v>10.344</v>
       </c>
       <c r="D32" t="n">
-        <v>1.211</v>
+        <v>3.281</v>
       </c>
       <c r="E32" t="n">
-        <v>2.211</v>
+        <v>5.031</v>
       </c>
       <c r="F32" t="n">
-        <v>0.842</v>
+        <v>0.156</v>
       </c>
       <c r="G32" t="n">
-        <v>2.579</v>
+        <v>0.469</v>
       </c>
       <c r="H32" t="n">
-        <v>0.263</v>
+        <v>3.312</v>
       </c>
       <c r="I32" t="n">
-        <v>0.579</v>
+        <v>5.094</v>
       </c>
       <c r="J32" t="n">
-        <v>0.947</v>
+        <v>1.031</v>
       </c>
       <c r="K32" t="n">
-        <v>0.526</v>
+        <v>2.062</v>
       </c>
       <c r="L32" t="n">
-        <v>0.421</v>
+        <v>1.312</v>
       </c>
       <c r="M32" t="n">
-        <v>0.579</v>
+        <v>0.344</v>
       </c>
       <c r="N32" t="n">
-        <v>0.526</v>
+        <v>1.094</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.632</v>
+        <v>1.281</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.632</v>
+        <v>1.281</v>
       </c>
       <c r="R32" t="n">
-        <v>1.632</v>
+        <v>2.969</v>
       </c>
       <c r="S32" t="n">
-        <v>0.632</v>
+        <v>4.125</v>
       </c>
       <c r="T32" t="n">
-        <v>67</v>
+        <v>391</v>
       </c>
       <c r="U32" t="n">
         <v>1</v>
       </c>
       <c r="V32" t="n">
-        <v>0.368</v>
+        <v>1.688</v>
       </c>
       <c r="W32" t="n">
-        <v>0.526</v>
+        <v>0.375</v>
       </c>
       <c r="X32" t="n">
-        <v>0.263</v>
+        <v>0.281</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.947</v>
+        <v>5.562</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.474</v>
+        <v>7.875</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.643</v>
+        <v>0.706</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.368</v>
+        <v>0.969</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.789</v>
+        <v>1.75</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.467</v>
+        <v>0.554</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.158</v>
+        <v>0.062</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.526</v>
+        <v>0.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.3</v>
+        <v>0.125</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.632</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.316</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.211</v>
+        <v>0.156</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.263</v>
+        <v>0.469</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.167</v>
+        <v>0.333</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>5.676</v>
+        <v>9.022</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.516</v>
+        <v>0.639</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.516</v>
+        <v>0.668</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.918</v>
+        <v>1.146</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.111</v>
+        <v>0.142</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.055</v>
+        <v>0.602</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.5</v>
+        <v>0.805</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.193</v>
+        <v>0.206</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.034</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.048</v>
+        <v>0.127</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.033</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#2 O. BALCEROWSKI (Per Game)</t>
+          <t>#3 J. WEBB (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C33" t="n">
-        <v>10.607</v>
+        <v>9.4</v>
       </c>
       <c r="D33" t="n">
-        <v>3.429</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>5.25</v>
+        <v>3.7</v>
       </c>
       <c r="F33" t="n">
-        <v>0.179</v>
+        <v>1.3</v>
       </c>
       <c r="G33" t="n">
-        <v>0.464</v>
+        <v>3.033</v>
       </c>
       <c r="H33" t="n">
-        <v>3.214</v>
+        <v>1.5</v>
       </c>
       <c r="I33" t="n">
-        <v>4.857</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
-        <v>1.071</v>
+        <v>0.667</v>
       </c>
       <c r="K33" t="n">
-        <v>2.143</v>
+        <v>3.067</v>
       </c>
       <c r="L33" t="n">
-        <v>1.214</v>
+        <v>0.767</v>
       </c>
       <c r="M33" t="n">
-        <v>0.393</v>
+        <v>0.667</v>
       </c>
       <c r="N33" t="n">
-        <v>1.143</v>
+        <v>0.3</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.393</v>
+        <v>1.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.393</v>
+        <v>1.3</v>
       </c>
       <c r="R33" t="n">
-        <v>2.893</v>
+        <v>2.467</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>1.867</v>
       </c>
       <c r="T33" t="n">
-        <v>351</v>
+        <v>274</v>
       </c>
       <c r="U33" t="n">
-        <v>1.071</v>
+        <v>0.6</v>
       </c>
       <c r="V33" t="n">
-        <v>1.429</v>
+        <v>0.6</v>
       </c>
       <c r="W33" t="n">
-        <v>0.429</v>
+        <v>0.733</v>
       </c>
       <c r="X33" t="n">
-        <v>0.321</v>
+        <v>0.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>5.607</v>
+        <v>2.6</v>
       </c>
       <c r="Z33" t="n">
-        <v>7.821</v>
+        <v>3.433</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.717</v>
+        <v>0.757</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.964</v>
+        <v>0.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.786</v>
+        <v>1.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.54</v>
+        <v>0.417</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.5</v>
+        <v>0.967</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.143</v>
+        <v>0.414</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>0.367</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.179</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.464</v>
+        <v>2.2</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.385</v>
+        <v>0.424</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>9.244</v>
+        <v>8.869</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.647</v>
+        <v>0.587</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.675</v>
+        <v>0.621</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.147</v>
+        <v>1.06</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.151</v>
+        <v>0.147</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.223</v>
       </c>
       <c r="AU33" t="n">
-        <v>0.769</v>
+        <v>0.513</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.211</v>
+        <v>0.198</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.067</v>
+        <v>0.041</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.132</v>
+        <v>0.184</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.04</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#3 J. WEBB (Per Game)</t>
+          <t>#4 T. KALINOSKI (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C34" t="n">
-        <v>9.115</v>
+        <v>6.276</v>
       </c>
       <c r="D34" t="n">
-        <v>2.077</v>
+        <v>0.897</v>
       </c>
       <c r="E34" t="n">
-        <v>3.5</v>
+        <v>2.241</v>
       </c>
       <c r="F34" t="n">
-        <v>1.192</v>
+        <v>1.241</v>
       </c>
       <c r="G34" t="n">
-        <v>2.885</v>
+        <v>3.897</v>
       </c>
       <c r="H34" t="n">
-        <v>1.385</v>
+        <v>0.759</v>
       </c>
       <c r="I34" t="n">
-        <v>1.692</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>0.654</v>
+        <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>3.038</v>
+        <v>1.517</v>
       </c>
       <c r="L34" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.897</v>
       </c>
       <c r="M34" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.897</v>
       </c>
       <c r="N34" t="n">
-        <v>0.308</v>
+        <v>0.414</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.269</v>
+        <v>0.759</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.269</v>
+        <v>0.759</v>
       </c>
       <c r="R34" t="n">
-        <v>2.5</v>
+        <v>2.724</v>
       </c>
       <c r="S34" t="n">
-        <v>1.846</v>
+        <v>0.828</v>
       </c>
       <c r="T34" t="n">
-        <v>238</v>
+        <v>148</v>
       </c>
       <c r="U34" t="n">
-        <v>0.538</v>
+        <v>1</v>
       </c>
       <c r="V34" t="n">
-        <v>0.577</v>
+        <v>0.586</v>
       </c>
       <c r="W34" t="n">
-        <v>0.846</v>
+        <v>0.241</v>
       </c>
       <c r="X34" t="n">
-        <v>0.462</v>
+        <v>0.138</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.462</v>
+        <v>1.034</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.115</v>
+        <v>1.552</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.79</v>
+        <v>0.667</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.577</v>
+        <v>0.138</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.192</v>
+        <v>0.655</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.484</v>
+        <v>0.211</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.423</v>
+        <v>0.483</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.885</v>
+        <v>1.034</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.478</v>
+        <v>0.467</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.269</v>
+        <v>0.138</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.731</v>
+        <v>0.793</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.368</v>
+        <v>0.174</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.923</v>
+        <v>1.103</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.154</v>
+        <v>3.103</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.429</v>
+        <v>0.356</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>8.398</v>
+        <v>7.337</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.605</v>
+        <v>0.449</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.639</v>
+        <v>0.477</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.085</v>
+        <v>0.855</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.151</v>
+        <v>0.103</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.217</v>
+        <v>0.124</v>
       </c>
       <c r="AU34" t="n">
-        <v>0.515</v>
+        <v>2.636</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.197</v>
+        <v>0.175</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.039</v>
+        <v>0.051</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.193</v>
+        <v>0.098</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.024</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#4 T. KALINOSKI (Per Game)</t>
+          <t>#7 J. BARREIRO (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C35" t="n">
-        <v>6.52</v>
+        <v>4.194</v>
       </c>
       <c r="D35" t="n">
-        <v>0.92</v>
+        <v>0.71</v>
       </c>
       <c r="E35" t="n">
-        <v>2.28</v>
+        <v>1.258</v>
       </c>
       <c r="F35" t="n">
-        <v>1.28</v>
+        <v>0.677</v>
       </c>
       <c r="G35" t="n">
-        <v>3.84</v>
+        <v>2.452</v>
       </c>
       <c r="H35" t="n">
-        <v>0.84</v>
+        <v>0.742</v>
       </c>
       <c r="I35" t="n">
-        <v>1.08</v>
+        <v>1.161</v>
       </c>
       <c r="J35" t="n">
-        <v>2.24</v>
+        <v>0.581</v>
       </c>
       <c r="K35" t="n">
-        <v>1.44</v>
+        <v>2.032</v>
       </c>
       <c r="L35" t="n">
-        <v>0.92</v>
+        <v>0.774</v>
       </c>
       <c r="M35" t="n">
-        <v>0.96</v>
+        <v>0.548</v>
       </c>
       <c r="N35" t="n">
-        <v>0.4</v>
+        <v>0.194</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.76</v>
+        <v>0.387</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.76</v>
+        <v>0.387</v>
       </c>
       <c r="R35" t="n">
-        <v>2.56</v>
+        <v>1.226</v>
       </c>
       <c r="S35" t="n">
-        <v>0.92</v>
+        <v>1.161</v>
       </c>
       <c r="T35" t="n">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="U35" t="n">
-        <v>1.04</v>
+        <v>0.29</v>
       </c>
       <c r="V35" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.032</v>
       </c>
       <c r="W35" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="X35" t="n">
-        <v>0.16</v>
+        <v>0.129</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.64</v>
+        <v>1.903</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.678</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.16</v>
+        <v>0.161</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.68</v>
+        <v>0.387</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.235</v>
+        <v>0.417</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.04</v>
+        <v>0.129</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.16</v>
+        <v>0.258</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.19</v>
+        <v>0.258</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.12</v>
+        <v>0.419</v>
       </c>
       <c r="AL35" t="n">
-        <v>3</v>
+        <v>1.452</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.373</v>
+        <v>0.289</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>7.355</v>
+        <v>4.608</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.464</v>
+        <v>0.465</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.494</v>
+        <v>0.497</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.886</v>
+        <v>0.91</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.103</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.137</v>
+        <v>0.2</v>
       </c>
       <c r="AU35" t="n">
-        <v>2.947</v>
+        <v>1.5</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.176</v>
+        <v>0.132</v>
       </c>
       <c r="AW35" t="n">
         <v>0.053</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.093</v>
+        <v>0.157</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.079</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#7 J. BARREIRO (Per Game)</t>
+          <t>#9 A. DÍAZ (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C36" t="n">
-        <v>3.963</v>
+        <v>5.733</v>
       </c>
       <c r="D36" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.367</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.433</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.967</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M36" t="n">
         <v>0.667</v>
       </c>
-      <c r="E36" t="n">
-        <v>1.222</v>
-      </c>
-      <c r="F36" t="n">
+      <c r="N36" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.533</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.067</v>
+      </c>
+      <c r="T36" t="n">
+        <v>286</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.433</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="AK36" t="n">
         <v>0.667</v>
       </c>
-      <c r="G36" t="n">
-        <v>2.296</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1.037</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1.481</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.704</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.259</v>
-      </c>
-      <c r="S36" t="n">
-        <v>1.111</v>
-      </c>
-      <c r="T36" t="n">
-        <v>116</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0.926</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="Y36" t="n">
+      <c r="AL36" t="n">
+        <v>2.067</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>19:42</t>
+        </is>
+      </c>
+      <c r="AO36" t="n">
+        <v>4.993</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="AR36" t="n">
         <v>1.148</v>
       </c>
-      <c r="Z36" t="n">
-        <v>1.741</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0.407</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0.259</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0.259</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0.407</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.296</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AO36" t="n">
-        <v>4.345</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>0.499</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>0.912</v>
-      </c>
       <c r="AS36" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.107</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.179</v>
+        <v>0.342</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.6</v>
+        <v>5.562</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.129</v>
+        <v>0.116</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.05</v>
+        <v>0.033</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.119</v>
+        <v>0.113</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.02</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#9 A. DÍAZ (Per Game)</t>
+          <t>#11 J. COBBS (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C37" t="n">
-        <v>5.346</v>
+        <v>5.923</v>
       </c>
       <c r="D37" t="n">
-        <v>0.731</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>1.346</v>
+        <v>1.615</v>
       </c>
       <c r="F37" t="n">
-        <v>0.885</v>
+        <v>0.923</v>
       </c>
       <c r="G37" t="n">
-        <v>2.269</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="T37" t="n">
+        <v>80</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.538</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="AF37" t="n">
         <v>1.231</v>
       </c>
-      <c r="I37" t="n">
-        <v>1.385</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2.923</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1.731</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0.423</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0.423</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.462</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1.923</v>
-      </c>
-      <c r="T37" t="n">
-        <v>237</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0.538</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.385</v>
-      </c>
-      <c r="Z37" t="n">
+      <c r="AG37" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="AL37" t="n">
         <v>1.615</v>
       </c>
-      <c r="AA37" t="n">
-        <v>0.857</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0.192</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0.8080000000000001</v>
-      </c>
-      <c r="AG37" t="n">
+      <c r="AM37" t="n">
         <v>0.476</v>
       </c>
-      <c r="AH37" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.962</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0.333</v>
-      </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>19:27</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>4.648</v>
+        <v>4.345</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.569</v>
+        <v>0.66</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.633</v>
+        <v>0.707</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.15</v>
+        <v>1.363</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.091</v>
+        <v>0.035</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.34</v>
+        <v>0.319</v>
       </c>
       <c r="AU37" t="n">
-        <v>6.909</v>
+        <v>6</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.109</v>
+        <v>0.179</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.11</v>
+        <v>0.094</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.102</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#11 J. COBBS (Per Game)</t>
+          <t>#13 X. CASTAÑEDA (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>6.778</v>
+        <v>0.714</v>
       </c>
       <c r="D38" t="n">
-        <v>1.111</v>
+        <v>0.143</v>
       </c>
       <c r="E38" t="n">
-        <v>1.889</v>
+        <v>1.429</v>
       </c>
       <c r="F38" t="n">
-        <v>1.222</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>2.222</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0.889</v>
+        <v>0.429</v>
       </c>
       <c r="I38" t="n">
-        <v>0.889</v>
+        <v>0.571</v>
       </c>
       <c r="J38" t="n">
-        <v>1.111</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>0.667</v>
+        <v>0.143</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="M38" t="n">
-        <v>0.222</v>
+        <v>0.286</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.111</v>
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.111</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="T38" t="n">
+        <v>-6</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
         <v>1</v>
       </c>
-      <c r="S38" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="T38" t="n">
-        <v>59</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.111</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.222</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="AD38" t="n">
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="AO38" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="AU38" t="n">
         <v>1</v>
       </c>
-      <c r="AE38" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AO38" t="n">
-        <v>4.613</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0.716</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0.753</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.469</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>10</v>
-      </c>
       <c r="AV38" t="n">
-        <v>0.175</v>
+        <v>0.217</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.068</v>
+        <v>0.023</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.04</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#13 X. CASTAÑEDA (Per Game)</t>
+          <t>#14 N. DJEDOVIC (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C39" t="n">
+        <v>8.571</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2.571</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" t="n">
         <v>0.714</v>
       </c>
-      <c r="D39" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="E39" t="n">
-        <v>1.429</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>2.476</v>
       </c>
       <c r="H39" t="n">
-        <v>0.429</v>
+        <v>1.286</v>
       </c>
       <c r="I39" t="n">
-        <v>0.571</v>
+        <v>2.048</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0.714</v>
       </c>
       <c r="K39" t="n">
-        <v>0.143</v>
+        <v>1.857</v>
       </c>
       <c r="L39" t="n">
-        <v>0.143</v>
+        <v>0.619</v>
       </c>
       <c r="M39" t="n">
-        <v>0.286</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N39" t="n">
         <v>0.286</v>
@@ -6288,1396 +6288,1396 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
+        <v>1.429</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.429</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.524</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.524</v>
+      </c>
+      <c r="T39" t="n">
+        <v>157</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.619</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.619</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.857</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="AB39" t="n">
         <v>1</v>
       </c>
-      <c r="Q39" t="n">
-        <v>1</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.143</v>
-      </c>
-      <c r="S39" t="n">
-        <v>1.143</v>
-      </c>
-      <c r="T39" t="n">
-        <v>-6</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
       <c r="AC39" t="n">
-        <v>0.286</v>
+        <v>1.667</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.143</v>
+        <v>0.238</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.143</v>
+        <v>0.524</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.125</v>
+        <v>0.455</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>0.238</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>0.381</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>0.476</v>
       </c>
       <c r="AL39" t="n">
-        <v>1</v>
+        <v>2.095</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>0.227</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>3.68</v>
+        <v>8.805999999999999</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.059</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.133</v>
+        <v>0.581</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.194</v>
+        <v>0.973</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.272</v>
+        <v>0.162</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.176</v>
+        <v>0.199</v>
       </c>
       <c r="AU39" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.216</v>
+        <v>0.225</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.02</v>
+        <v>0.038</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.023</v>
+        <v>0.128</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.033</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#14 N. DJEDOVIC (Per Game)</t>
+          <t>#19 E. SULEJMANOVIC (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C40" t="n">
-        <v>8.571</v>
+        <v>6.31</v>
       </c>
       <c r="D40" t="n">
-        <v>2.571</v>
+        <v>1.828</v>
       </c>
       <c r="E40" t="n">
-        <v>4</v>
+        <v>3.172</v>
       </c>
       <c r="F40" t="n">
-        <v>0.714</v>
+        <v>0.655</v>
       </c>
       <c r="G40" t="n">
-        <v>2.476</v>
+        <v>1.828</v>
       </c>
       <c r="H40" t="n">
-        <v>1.286</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>2.048</v>
+        <v>1.586</v>
       </c>
       <c r="J40" t="n">
-        <v>0.714</v>
+        <v>0.966</v>
       </c>
       <c r="K40" t="n">
-        <v>1.857</v>
+        <v>2.862</v>
       </c>
       <c r="L40" t="n">
-        <v>0.619</v>
+        <v>1.448</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="N40" t="n">
-        <v>0.286</v>
+        <v>0.483</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.429</v>
+        <v>0.828</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.429</v>
+        <v>0.828</v>
       </c>
       <c r="R40" t="n">
-        <v>1.524</v>
+        <v>2.276</v>
       </c>
       <c r="S40" t="n">
-        <v>1.524</v>
+        <v>1.552</v>
       </c>
       <c r="T40" t="n">
-        <v>157</v>
+        <v>215</v>
       </c>
       <c r="U40" t="n">
-        <v>1.619</v>
+        <v>0.586</v>
       </c>
       <c r="V40" t="n">
-        <v>0.381</v>
+        <v>1.034</v>
       </c>
       <c r="W40" t="n">
-        <v>0.857</v>
+        <v>0.172</v>
       </c>
       <c r="X40" t="n">
-        <v>0.476</v>
+        <v>0.103</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.619</v>
+        <v>1.655</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.857</v>
+        <v>2.759</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.679</v>
+        <v>0.6</v>
       </c>
       <c r="AB40" t="n">
-        <v>1</v>
+        <v>0.759</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.667</v>
+        <v>1.517</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.238</v>
+        <v>0.103</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.524</v>
+        <v>0.483</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.455</v>
+        <v>0.214</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.238</v>
+        <v>0.103</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.381</v>
+        <v>0.345</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.625</v>
+        <v>0.3</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.476</v>
+        <v>0.552</v>
       </c>
       <c r="AL40" t="n">
-        <v>2.095</v>
+        <v>1.483</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.227</v>
+        <v>0.372</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>8.805999999999999</v>
+        <v>6.526</v>
       </c>
       <c r="AP40" t="n">
         <v>0.5620000000000001</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.581</v>
+        <v>0.554</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.973</v>
+        <v>0.967</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.162</v>
+        <v>0.127</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.199</v>
+        <v>0.138</v>
       </c>
       <c r="AU40" t="n">
-        <v>0.5</v>
+        <v>1.167</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.224</v>
+        <v>0.203</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.038</v>
+        <v>0.107</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.128</v>
+        <v>0.239</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.026</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>#19 E. SULEJMANOVIC (Per Game)</t>
+          <t>#21 A. RUBIT (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C41" t="n">
-        <v>6.37</v>
+        <v>5.632</v>
       </c>
       <c r="D41" t="n">
-        <v>1.815</v>
+        <v>1.842</v>
       </c>
       <c r="E41" t="n">
-        <v>3.259</v>
+        <v>3.579</v>
       </c>
       <c r="F41" t="n">
-        <v>0.667</v>
+        <v>0.053</v>
       </c>
       <c r="G41" t="n">
-        <v>1.815</v>
+        <v>0.211</v>
       </c>
       <c r="H41" t="n">
-        <v>0.741</v>
+        <v>1.789</v>
       </c>
       <c r="I41" t="n">
-        <v>1.63</v>
+        <v>2.421</v>
       </c>
       <c r="J41" t="n">
-        <v>0.926</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>2.926</v>
+        <v>1.105</v>
       </c>
       <c r="L41" t="n">
-        <v>1.481</v>
+        <v>0.842</v>
       </c>
       <c r="M41" t="n">
-        <v>0.296</v>
+        <v>0.316</v>
       </c>
       <c r="N41" t="n">
-        <v>0.519</v>
+        <v>0.263</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.852</v>
+        <v>0.526</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.852</v>
+        <v>0.526</v>
       </c>
       <c r="R41" t="n">
-        <v>2.333</v>
+        <v>2.368</v>
       </c>
       <c r="S41" t="n">
-        <v>1.593</v>
+        <v>2</v>
       </c>
       <c r="T41" t="n">
-        <v>201</v>
+        <v>103</v>
       </c>
       <c r="U41" t="n">
-        <v>0.63</v>
+        <v>0.421</v>
       </c>
       <c r="V41" t="n">
-        <v>1.037</v>
+        <v>1.263</v>
       </c>
       <c r="W41" t="n">
-        <v>0.185</v>
+        <v>0.105</v>
       </c>
       <c r="X41" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2.474</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>3.526</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.474</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AO41" t="n">
+        <v>5.381</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AX41" t="n">
         <v>0.111</v>
       </c>
-      <c r="Y41" t="n">
-        <v>1.778</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.889</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.481</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>1.481</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AO41" t="n">
-        <v>6.643</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>0.959</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>1.087</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>0.245</v>
-      </c>
       <c r="AY41" t="n">
-        <v>0.033</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#21 A. RUBIT (Per Game)</t>
+          <t>#22 M. TRUJILLO (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C42" t="n">
-        <v>5.688</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>1.875</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>2.375</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6879999999999999</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="AO42" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
         <v>1</v>
       </c>
-      <c r="L42" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="R42" t="n">
-        <v>2.562</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2</v>
-      </c>
-      <c r="T42" t="n">
-        <v>83</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.312</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>2.438</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>3.438</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0.709</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0.9379999999999999</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AO42" t="n">
-        <v>5.482</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>0.508</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>0.578</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>1.037</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>0.103</v>
-      </c>
       <c r="AT42" t="n">
-        <v>0.452</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.222</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.205</v>
+        <v>0.114</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.079</v>
+        <v>0.272</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.101</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#22 M. TRUJILLO (Per Game)</t>
+          <t>#27 C. DUARTE (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
+        <v>27</v>
+      </c>
+      <c r="C43" t="n">
+        <v>11.444</v>
+      </c>
+      <c r="D43" t="n">
         <v>2</v>
       </c>
-      <c r="C43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>3.593</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1.593</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>4.444</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>2.667</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>2.963</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>2.889</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1.593</v>
       </c>
       <c r="L43" t="n">
-        <v>0.5</v>
+        <v>0.259</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>0.481</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.5</v>
+        <v>1.481</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.5</v>
+        <v>1.481</v>
       </c>
       <c r="R43" t="n">
-        <v>0.5</v>
+        <v>2.037</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.074</v>
       </c>
       <c r="T43" t="n">
-        <v>-1</v>
+        <v>327</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2.037</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>0.519</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>3.593</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>4.222</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>0.851</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>0.704</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.259</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.074</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>0.345</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>0.529</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.259</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>3.815</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>0.5</v>
+        <v>10.822</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>0.546</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>0.613</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.057</v>
       </c>
       <c r="AS43" t="n">
-        <v>1</v>
+        <v>0.137</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>0.332</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.114</v>
+        <v>0.276</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.275</v>
+        <v>0.016</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>0.109</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#27 C. DUARTE (Per Game)</t>
+          <t>#33 K. TILLIE (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C44" t="n">
-        <v>11.615</v>
+        <v>5.542</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>0.833</v>
       </c>
       <c r="E44" t="n">
-        <v>3.577</v>
+        <v>1.875</v>
       </c>
       <c r="F44" t="n">
-        <v>1.615</v>
+        <v>1.167</v>
       </c>
       <c r="G44" t="n">
-        <v>4.5</v>
+        <v>3.292</v>
       </c>
       <c r="H44" t="n">
-        <v>2.769</v>
+        <v>0.375</v>
       </c>
       <c r="I44" t="n">
-        <v>3.038</v>
+        <v>0.667</v>
       </c>
       <c r="J44" t="n">
-        <v>2.962</v>
+        <v>0.875</v>
       </c>
       <c r="K44" t="n">
-        <v>1.654</v>
+        <v>1.417</v>
       </c>
       <c r="L44" t="n">
-        <v>0.231</v>
+        <v>1.042</v>
       </c>
       <c r="M44" t="n">
-        <v>0.654</v>
+        <v>0.625</v>
       </c>
       <c r="N44" t="n">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1.538</v>
+        <v>0.792</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.538</v>
+        <v>0.792</v>
       </c>
       <c r="R44" t="n">
         <v>2</v>
       </c>
       <c r="S44" t="n">
-        <v>3.154</v>
+        <v>0.958</v>
       </c>
       <c r="T44" t="n">
-        <v>325</v>
+        <v>110</v>
       </c>
       <c r="U44" t="n">
-        <v>1.962</v>
+        <v>0.417</v>
       </c>
       <c r="V44" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.625</v>
       </c>
       <c r="W44" t="n">
-        <v>0.846</v>
+        <v>0.25</v>
       </c>
       <c r="X44" t="n">
-        <v>0.538</v>
+        <v>0.125</v>
       </c>
       <c r="Y44" t="n">
-        <v>3.692</v>
+        <v>0.792</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.308</v>
+        <v>1.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.857</v>
+        <v>0.528</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.333</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.269</v>
+        <v>0.667</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.545</v>
+        <v>0.5</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.385</v>
+        <v>0.083</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.038</v>
+        <v>0.375</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.37</v>
+        <v>0.222</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.346</v>
+        <v>0.292</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.654</v>
+        <v>0.958</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.529</v>
+        <v>0.304</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.269</v>
+        <v>0.875</v>
       </c>
       <c r="AL44" t="n">
-        <v>3.846</v>
+        <v>2.333</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.33</v>
+        <v>0.375</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>10.952</v>
+        <v>6.252</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.548</v>
+        <v>0.5</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.617</v>
+        <v>0.507</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.061</v>
+        <v>0.886</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.14</v>
+        <v>0.127</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.343</v>
+        <v>0.073</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.925</v>
+        <v>1.105</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.274</v>
+        <v>0.206</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.014</v>
+        <v>0.082</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.112</v>
+        <v>0.126</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.111</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>#33 K. TILLIE (Per Game)</t>
+          <t>#45 D. KRAVISH (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C45" t="n">
-        <v>6.045</v>
+        <v>5.444</v>
       </c>
       <c r="D45" t="n">
-        <v>0.909</v>
+        <v>2.222</v>
       </c>
       <c r="E45" t="n">
-        <v>1.955</v>
+        <v>4.667</v>
       </c>
       <c r="F45" t="n">
-        <v>1.273</v>
+        <v>0.222</v>
       </c>
       <c r="G45" t="n">
-        <v>3.455</v>
+        <v>1.444</v>
       </c>
       <c r="H45" t="n">
-        <v>0.409</v>
+        <v>0.333</v>
       </c>
       <c r="I45" t="n">
-        <v>0.727</v>
+        <v>0.444</v>
       </c>
       <c r="J45" t="n">
-        <v>0.955</v>
+        <v>1.444</v>
       </c>
       <c r="K45" t="n">
-        <v>1.5</v>
+        <v>1.667</v>
       </c>
       <c r="L45" t="n">
-        <v>1.091</v>
+        <v>0.889</v>
       </c>
       <c r="M45" t="n">
-        <v>0.591</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0.364</v>
+        <v>0.222</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.727</v>
+        <v>1.444</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.727</v>
+        <v>1.444</v>
       </c>
       <c r="R45" t="n">
-        <v>2.045</v>
+        <v>1.778</v>
       </c>
       <c r="S45" t="n">
-        <v>1.045</v>
+        <v>0.889</v>
       </c>
       <c r="T45" t="n">
-        <v>116</v>
+        <v>32</v>
       </c>
       <c r="U45" t="n">
-        <v>0.455</v>
+        <v>0.333</v>
       </c>
       <c r="V45" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.889</v>
       </c>
       <c r="W45" t="n">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0.136</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.864</v>
+        <v>0.889</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.636</v>
+        <v>1</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.528</v>
+        <v>0.889</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.364</v>
+        <v>0.667</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.636</v>
+        <v>1.111</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.571</v>
+        <v>0.6</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.091</v>
+        <v>1</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.409</v>
+        <v>3</v>
       </c>
       <c r="AG45" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="n">
         <v>0.222</v>
       </c>
-      <c r="AH45" t="n">
-        <v>0.318</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>1.045</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>0.304</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>0.955</v>
-      </c>
       <c r="AL45" t="n">
-        <v>2.409</v>
+        <v>1.444</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.396</v>
+        <v>0.154</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>6.456</v>
+        <v>7.751</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.521</v>
+        <v>0.418</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.528</v>
+        <v>0.432</v>
       </c>
       <c r="AR45" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.702</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.113</v>
+        <v>0.186</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.076</v>
+        <v>0.055</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.312</v>
+        <v>1</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.205</v>
+        <v>0.22</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.083</v>
+        <v>0.06</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.129</v>
+        <v>0.127</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.034</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>#45 D. KRAVISH (Per Game)</t>
+          <t>#55 K. PERRY (Per Game)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>11.156</v>
       </c>
       <c r="D46" t="n">
-        <v>2.2</v>
+        <v>1.906</v>
       </c>
       <c r="E46" t="n">
-        <v>4.2</v>
+        <v>4.156</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4</v>
+        <v>1.812</v>
       </c>
       <c r="G46" t="n">
-        <v>1.4</v>
+        <v>4.438</v>
       </c>
       <c r="H46" t="n">
-        <v>0.4</v>
+        <v>1.906</v>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>2.406</v>
       </c>
       <c r="J46" t="n">
-        <v>1.4</v>
+        <v>4.562</v>
       </c>
       <c r="K46" t="n">
-        <v>2</v>
+        <v>1.469</v>
       </c>
       <c r="L46" t="n">
-        <v>0.8</v>
+        <v>0.375</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>1.531</v>
       </c>
       <c r="N46" t="n">
-        <v>0.2</v>
+        <v>0.375</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.8</v>
+        <v>1.531</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.8</v>
+        <v>1.531</v>
       </c>
       <c r="R46" t="n">
-        <v>2</v>
+        <v>2.312</v>
       </c>
       <c r="S46" t="n">
-        <v>0.2</v>
+        <v>3.312</v>
       </c>
       <c r="T46" t="n">
-        <v>24</v>
+        <v>434</v>
       </c>
       <c r="U46" t="n">
-        <v>0.6</v>
+        <v>1.375</v>
       </c>
       <c r="V46" t="n">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>0.531</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.2</v>
+        <v>2.875</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.2</v>
+        <v>3.531</v>
       </c>
       <c r="AA46" t="n">
-        <v>1</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.8</v>
+        <v>0.438</v>
       </c>
       <c r="AC46" t="n">
-        <v>1</v>
+        <v>1.406</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.8</v>
+        <v>0.311</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.4</v>
+        <v>1.625</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.25</v>
+        <v>0.308</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.4</v>
+        <v>1.719</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.4</v>
+        <v>4.25</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.286</v>
+        <v>0.404</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>22:17</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>6.576</v>
+        <v>11.184</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.5</v>
+        <v>0.538</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.519</v>
+        <v>0.578</v>
       </c>
       <c r="AR46" t="n">
-        <v>0.912</v>
+        <v>0.998</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.122</v>
+        <v>0.137</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.222</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.75</v>
+        <v>2.98</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.191</v>
+        <v>0.23</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.056</v>
+        <v>0.018</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.158</v>
+        <v>0.081</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.05</v>
+        <v>0.173</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>#55 K. PERRY (Per Game)</t>
+          <t>#56 A. BUTAJEVAS (Per Game)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>10.643</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>1.857</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>4.036</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>1.714</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>4.286</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1.786</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>2.321</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>4.357</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1.464</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0.357</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1.429</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0.357</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1.429</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.429</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.357</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>3.214</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.571</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>0.857</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.643</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.321</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.796</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.464</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.464</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.317</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.536</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.571</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.341</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.107</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.214</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.607</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>4.071</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.395</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>21:48</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>10.771</v>
+        <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="AR47" t="n">
-        <v>0.988</v>
+        <v>0</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.133</v>
+        <v>0</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.215</v>
+        <v>0</v>
       </c>
       <c r="AU47" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV47" t="n">
-        <v>0.226</v>
+        <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.162</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>#56 A. BUTAJEVAS (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -7704,10 +7704,10 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.094</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -7719,13 +7719,13 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.062</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>0.156</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO48" t="n">
@@ -7832,157 +7832,157 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>87.125</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>19.344</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>35.688</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>10.75</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>30.031</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>16.188</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>22.688</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>18.312</v>
       </c>
       <c r="K49" t="n">
-        <v>1.821</v>
+        <v>24.031</v>
       </c>
       <c r="L49" t="n">
-        <v>1.107</v>
+        <v>10.969</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>7.562</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.781</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1.107</v>
+        <v>12.281</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>11.219</v>
       </c>
       <c r="R49" t="n">
-        <v>0.179</v>
+        <v>23.938</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>22.406</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>3099</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>10.812</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>9.311999999999999</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>5.156</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>26.125</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>36.25</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>0.721</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>5.688</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>11.875</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>0.479</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>3.719</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>10.25</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>0.363</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>2.531</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>6.375</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>0.397</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>8.218999999999999</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>23.656</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>0.347</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>201:33</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>0</v>
+        <v>87.983</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>0.575</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>0.246</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>1.491</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>0.147</v>
       </c>
       <c r="AY49" t="n">
         <v>0</v>
@@ -7991,477 +7991,159 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>86.90600000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>19.469</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>34.344</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>9.406000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>26.031</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>19.75</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>25.594</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>16.938</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>25.969</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>8.625</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>6.094</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4.875</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>12.375</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>22.562</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>23.875</v>
       </c>
       <c r="T50" t="n">
-        <v>46</v>
+        <v>3212</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>9.875</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>8.688000000000001</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>5.156</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>2.938</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>30.531</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>39.719</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>0.769</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>5.656</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>12.125</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>0.466</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>3.031</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>8.093999999999999</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>3.094</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>7.156</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>0.432</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>6.312</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>18.875</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>0.334</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>201:33</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>1.107</v>
+        <v>84.636</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>0.607</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>1.027</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>0.327</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>1.303</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>0.192</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>0.159</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>28</v>
-      </c>
-      <c r="C51" t="n">
-        <v>87.679</v>
-      </c>
-      <c r="D51" t="n">
-        <v>19.607</v>
-      </c>
-      <c r="E51" t="n">
-        <v>35.821</v>
-      </c>
-      <c r="F51" t="n">
-        <v>10.786</v>
-      </c>
-      <c r="G51" t="n">
-        <v>29.857</v>
-      </c>
-      <c r="H51" t="n">
-        <v>16.107</v>
-      </c>
-      <c r="I51" t="n">
-        <v>22.321</v>
-      </c>
-      <c r="J51" t="n">
-        <v>18.536</v>
-      </c>
-      <c r="K51" t="n">
-        <v>23.893</v>
-      </c>
-      <c r="L51" t="n">
-        <v>10.929</v>
-      </c>
-      <c r="M51" t="n">
-        <v>7.571</v>
-      </c>
-      <c r="N51" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>11.143</v>
-      </c>
-      <c r="R51" t="n">
-        <v>24.107</v>
-      </c>
-      <c r="S51" t="n">
-        <v>22.214</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2736</v>
-      </c>
-      <c r="U51" t="n">
-        <v>11.429</v>
-      </c>
-      <c r="V51" t="n">
-        <v>9.356999999999999</v>
-      </c>
-      <c r="W51" t="n">
-        <v>5.536</v>
-      </c>
-      <c r="X51" t="n">
-        <v>3.179</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>26.357</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>36.286</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0.726</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>5.714</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>3.643</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>9.856999999999999</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>8.286</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>23.357</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>200:53</t>
-        </is>
-      </c>
-      <c r="AO51" t="n">
-        <v>87.75</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0.581</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>0.999</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>1.513</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>28</v>
-      </c>
-      <c r="C52" t="n">
-        <v>85.75</v>
-      </c>
-      <c r="D52" t="n">
-        <v>18.571</v>
-      </c>
-      <c r="E52" t="n">
-        <v>33.107</v>
-      </c>
-      <c r="F52" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G52" t="n">
-        <v>26.214</v>
-      </c>
-      <c r="H52" t="n">
-        <v>20.107</v>
-      </c>
-      <c r="I52" t="n">
-        <v>26.179</v>
-      </c>
-      <c r="J52" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="K52" t="n">
-        <v>25.464</v>
-      </c>
-      <c r="L52" t="n">
-        <v>8.536</v>
-      </c>
-      <c r="M52" t="n">
-        <v>6</v>
-      </c>
-      <c r="N52" t="n">
-        <v>4.857</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>13.357</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>12.679</v>
-      </c>
-      <c r="R52" t="n">
-        <v>22.393</v>
-      </c>
-      <c r="S52" t="n">
-        <v>24.071</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2747</v>
-      </c>
-      <c r="U52" t="n">
-        <v>9.786</v>
-      </c>
-      <c r="V52" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W52" t="n">
-        <v>5.214</v>
-      </c>
-      <c r="X52" t="n">
-        <v>2.857</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>30.607</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>39.786</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0.769</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>11.679</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>2.821</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>7.821</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>3.071</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>7.321</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>6.429</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>18.893</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>200:53</t>
-        </is>
-      </c>
-      <c r="AO52" t="n">
-        <v>84.197</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>0.553</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>1.018</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>0.339</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>1.235</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>0.192</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="AY52" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Unicaja.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Unicaja.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2464.440000000001</v>
+        <v>2620.120000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>2448.4</v>
+        <v>2600.96</v>
       </c>
       <c r="D2" t="n">
-        <v>113.8702826335566</v>
+        <v>114.496186023622</v>
       </c>
       <c r="E2" t="n">
-        <v>113.5843816369874</v>
+        <v>113.650344488189</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5397051830718022</v>
+        <v>0.5396083667111704</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1395874179524337</v>
+        <v>0.1399545230908341</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2969543147208122</v>
+        <v>0.3084260731319555</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2463147883975274</v>
+        <v>0.2461059190031153</v>
       </c>
       <c r="J2" t="n">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="K2" t="n">
-        <v>298</v>
+        <v>326</v>
       </c>
       <c r="L2" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="M2" t="n">
+        <v>386</v>
+      </c>
+      <c r="N2" t="n">
+        <v>897</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1236</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.5500667556742324</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>192</v>
+      </c>
+      <c r="R2" t="n">
+        <v>411</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.1829105473965287</v>
+      </c>
+      <c r="T2" t="n">
+        <v>132</v>
+      </c>
+      <c r="U2" t="n">
         <v>359</v>
       </c>
-      <c r="N2" t="n">
-        <v>836</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1160</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.5515929624346172</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>182</v>
-      </c>
-      <c r="R2" t="n">
-        <v>380</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.1806942463147884</v>
-      </c>
-      <c r="T2" t="n">
-        <v>119</v>
-      </c>
-      <c r="U2" t="n">
-        <v>328</v>
-      </c>
       <c r="V2" t="n">
-        <v>0.1559676652401331</v>
+        <v>0.159768580329328</v>
       </c>
       <c r="W2" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="X2" t="n">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09700427960057062</v>
+        <v>0.09612817089452604</v>
       </c>
       <c r="Z2" t="n">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="AA2" t="n">
-        <v>757</v>
+        <v>798</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.359961959106039</v>
+        <v>0.3551401869158878</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7206896551724138</v>
+        <v>0.7257281553398058</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4789473684210526</v>
+        <v>0.4671532846715328</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3628048780487805</v>
+        <v>0.3676880222841226</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3970588235294117</v>
+        <v>0.3935185185185185</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3474240422721268</v>
+        <v>0.3483709273182957</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.441379310344828</v>
+        <v>1.451456310679612</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.725609756097561</v>
+        <v>0.7353760445682451</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.073881373569199</v>
+        <v>1.07396449704142</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8317307692307693</v>
+        <v>0.825</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.8490028490028491</v>
+        <v>0.8402061855670103</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.71875</v>
+        <v>1.75</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.491094147582697</v>
+        <v>1.503562945368171</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.351145038167939</v>
+        <v>5.33729216152019</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.842239185750636</v>
+        <v>6.840855106888361</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77.01375000000003</v>
+        <v>77.06235294117651</v>
       </c>
       <c r="C3" t="n">
-        <v>76.5125</v>
+        <v>76.49882352941177</v>
       </c>
       <c r="D3" t="n">
-        <v>113.8702826335566</v>
+        <v>114.4961860236221</v>
       </c>
       <c r="E3" t="n">
-        <v>113.5843816369874</v>
+        <v>113.650344488189</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5397051830718022</v>
+        <v>0.5396083667111704</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1395874179524337</v>
+        <v>0.1399545230908341</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2969543147208122</v>
+        <v>0.3084260731319555</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2463147883975274</v>
+        <v>0.2461059190031153</v>
       </c>
       <c r="J3" t="n">
-        <v>10.8125</v>
+        <v>10.67647058823529</v>
       </c>
       <c r="K3" t="n">
-        <v>9.3125</v>
+        <v>9.588235294117647</v>
       </c>
       <c r="L3" t="n">
-        <v>5.15625</v>
+        <v>5.147058823529412</v>
       </c>
       <c r="M3" t="n">
-        <v>11.21875</v>
+        <v>11.35294117647059</v>
       </c>
       <c r="N3" t="n">
-        <v>26.125</v>
+        <v>26.38235294117647</v>
       </c>
       <c r="O3" t="n">
-        <v>36.25</v>
+        <v>36.35294117647059</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5515929624346172</v>
+        <v>0.5500667556742322</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.6875</v>
+        <v>5.647058823529412</v>
       </c>
       <c r="R3" t="n">
-        <v>11.875</v>
+        <v>12.08823529411765</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1806942463147884</v>
+        <v>0.1829105473965287</v>
       </c>
       <c r="T3" t="n">
-        <v>3.71875</v>
+        <v>3.882352941176471</v>
       </c>
       <c r="U3" t="n">
-        <v>10.25</v>
+        <v>10.55882352941176</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1559676652401331</v>
+        <v>0.159768580329328</v>
       </c>
       <c r="W3" t="n">
-        <v>2.53125</v>
+        <v>2.5</v>
       </c>
       <c r="X3" t="n">
-        <v>6.375</v>
+        <v>6.352941176470588</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.09700427960057062</v>
+        <v>0.09612817089452602</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.21875</v>
+        <v>8.176470588235293</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.65625</v>
+        <v>23.47058823529412</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.359961959106039</v>
+        <v>0.3551401869158878</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7206896551724138</v>
+        <v>0.7257281553398058</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4789473684210526</v>
+        <v>0.4671532846715329</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3628048780487805</v>
+        <v>0.3676880222841226</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3970588235294117</v>
+        <v>0.3935185185185185</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3474240422721268</v>
+        <v>0.3483709273182957</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.441379310344828</v>
+        <v>1.451456310679612</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.725609756097561</v>
+        <v>0.7353760445682451</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.073881373569199</v>
+        <v>1.07396449704142</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8317307692307693</v>
+        <v>0.825</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.8490028490028491</v>
+        <v>0.8402061855670102</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.71875</v>
+        <v>1.75</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.491094147582697</v>
+        <v>1.503562945368171</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.351145038167939</v>
+        <v>5.33729216152019</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.842239185750636</v>
+        <v>6.840855106888362</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2432.36</v>
+        <v>2581.8</v>
       </c>
       <c r="C4" t="n">
-        <v>2448.4</v>
+        <v>2600.96</v>
       </c>
       <c r="D4" t="n">
-        <v>113.5843816369874</v>
+        <v>113.650344488189</v>
       </c>
       <c r="E4" t="n">
-        <v>113.8702826335566</v>
+        <v>114.496186023622</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5561594202898551</v>
+        <v>0.5576171875</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1535984876456601</v>
+        <v>0.1532673819144489</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2641148325358852</v>
+        <v>0.2603603603603604</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3271221532091098</v>
+        <v>0.328125</v>
       </c>
       <c r="J4" t="n">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="K4" t="n">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="L4" t="n">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="M4" t="n">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="N4" t="n">
-        <v>977</v>
+        <v>1030</v>
       </c>
       <c r="O4" t="n">
-        <v>1271</v>
+        <v>1338</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6578674948240165</v>
+        <v>0.6533203125</v>
       </c>
       <c r="Q4" t="n">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="R4" t="n">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2008281573498965</v>
+        <v>0.20361328125</v>
       </c>
       <c r="T4" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="U4" t="n">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1340579710144928</v>
+        <v>0.13818359375</v>
       </c>
       <c r="W4" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="X4" t="n">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1185300207039337</v>
+        <v>0.11474609375</v>
       </c>
       <c r="Z4" t="n">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="AA4" t="n">
-        <v>604</v>
+        <v>645</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3126293995859213</v>
+        <v>0.31494140625</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7686860739575138</v>
+        <v>0.7698056801195815</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4664948453608248</v>
+        <v>0.460431654676259</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3745173745173745</v>
+        <v>0.3639575971731449</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4323144104803494</v>
+        <v>0.4340425531914894</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3344370860927152</v>
+        <v>0.3472868217054264</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.537372147915028</v>
+        <v>1.539611360239163</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.749034749034749</v>
+        <v>0.7279151943462897</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.084033613445378</v>
+        <v>1.111363636363636</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8040712468193384</v>
+        <v>0.8123515439429929</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.007246376811594</v>
+        <v>1.013840830449827</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.75531914893617</v>
+        <v>1.757575757575758</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.302884615384615</v>
+        <v>1.290909090909091</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.644230769230769</v>
+        <v>4.654545454545454</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.947115384615385</v>
+        <v>5.945454545454545</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>76.01125</v>
+        <v>75.93529411764706</v>
       </c>
       <c r="C5" t="n">
-        <v>76.5125</v>
+        <v>76.49882352941177</v>
       </c>
       <c r="D5" t="n">
-        <v>113.5843816369874</v>
+        <v>113.650344488189</v>
       </c>
       <c r="E5" t="n">
-        <v>113.8702826335566</v>
+        <v>114.4961860236221</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5561594202898551</v>
+        <v>0.5576171875000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1535984876456601</v>
+        <v>0.1532673819144489</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2641148325358852</v>
+        <v>0.2603603603603604</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3271221532091098</v>
+        <v>0.328125</v>
       </c>
       <c r="J5" t="n">
-        <v>9.875</v>
+        <v>10.05882352941176</v>
       </c>
       <c r="K5" t="n">
-        <v>8.6875</v>
+        <v>8.617647058823529</v>
       </c>
       <c r="L5" t="n">
-        <v>5.15625</v>
+        <v>5.117647058823529</v>
       </c>
       <c r="M5" t="n">
-        <v>12.375</v>
+        <v>12.26470588235294</v>
       </c>
       <c r="N5" t="n">
-        <v>30.53125</v>
+        <v>30.29411764705882</v>
       </c>
       <c r="O5" t="n">
-        <v>39.71875</v>
+        <v>39.35294117647059</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6578674948240165</v>
+        <v>0.6533203125</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.65625</v>
+        <v>5.647058823529412</v>
       </c>
       <c r="R5" t="n">
-        <v>12.125</v>
+        <v>12.26470588235294</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2008281573498965</v>
+        <v>0.20361328125</v>
       </c>
       <c r="T5" t="n">
-        <v>3.03125</v>
+        <v>3.029411764705882</v>
       </c>
       <c r="U5" t="n">
-        <v>8.09375</v>
+        <v>8.323529411764707</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1340579710144928</v>
+        <v>0.13818359375</v>
       </c>
       <c r="W5" t="n">
-        <v>3.09375</v>
+        <v>3</v>
       </c>
       <c r="X5" t="n">
-        <v>7.15625</v>
+        <v>6.911764705882353</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1185300207039337</v>
+        <v>0.11474609375</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.3125</v>
+        <v>6.588235294117647</v>
       </c>
       <c r="AA5" t="n">
-        <v>18.875</v>
+        <v>18.97058823529412</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3126293995859213</v>
+        <v>0.31494140625</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7686860739575138</v>
+        <v>0.7698056801195815</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4664948453608248</v>
+        <v>0.460431654676259</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3745173745173745</v>
+        <v>0.3639575971731449</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4323144104803494</v>
+        <v>0.4340425531914893</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3344370860927152</v>
+        <v>0.3472868217054264</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.537372147915028</v>
+        <v>1.539611360239163</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.749034749034749</v>
+        <v>0.7279151943462897</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.084033613445378</v>
+        <v>1.111363636363636</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8040712468193384</v>
+        <v>0.8123515439429928</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.007246376811594</v>
+        <v>1.013840830449827</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.75531914893617</v>
+        <v>1.757575757575758</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.302884615384615</v>
+        <v>1.290909090909091</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.644230769230769</v>
+        <v>4.654545454545454</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.947115384615385</v>
+        <v>5.945454545454545</v>
       </c>
     </row>
     <row r="7">
@@ -1559,7 +1559,7 @@
         <v>0.667</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.191</v>
+        <v>0.189</v>
       </c>
       <c r="AW8" t="n">
         <v>0.129</v>
@@ -1568,7 +1568,7 @@
         <v>0.283</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="9">
@@ -1578,67 +1578,67 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="D9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F9" t="n">
+        <v>24</v>
+      </c>
+      <c r="G9" t="n">
+        <v>64</v>
+      </c>
+      <c r="H9" t="n">
+        <v>11</v>
+      </c>
+      <c r="I9" t="n">
         <v>22</v>
       </c>
-      <c r="G9" t="n">
-        <v>60</v>
-      </c>
-      <c r="H9" t="n">
-        <v>7</v>
-      </c>
-      <c r="I9" t="n">
-        <v>17</v>
-      </c>
       <c r="J9" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K9" t="n">
         <v>15</v>
       </c>
       <c r="L9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M9" t="n">
         <v>13</v>
       </c>
       <c r="N9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="R9" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="S9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T9" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="U9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W9" t="n">
         <v>14</v>
@@ -1647,87 +1647,87 @@
         <v>7</v>
       </c>
       <c r="Y9" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Z9" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AB9" t="n">
         <v>9</v>
       </c>
       <c r="AC9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.5</v>
+        <v>0.474</v>
       </c>
       <c r="AE9" t="n">
         <v>3</v>
       </c>
       <c r="AF9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.231</v>
+        <v>0.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI9" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.467</v>
+        <v>0.485</v>
       </c>
       <c r="AK9" t="n">
         <v>8</v>
       </c>
       <c r="AL9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.267</v>
+        <v>0.258</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>322:05</t>
+          <t>360:02</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>137.48</v>
+        <v>150.68</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.544</v>
+        <v>0.541</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.539</v>
+        <v>0.543</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.953</v>
+        <v>0.949</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.116</v>
+        <v>0.126</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.061</v>
+        <v>0.09</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.438</v>
+        <v>1.368</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.196</v>
+        <v>0.191</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.047</v>
+        <v>0.051</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.057</v>
+        <v>0.051</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.025</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="10">
@@ -1737,37 +1737,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="D10" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="E10" t="n">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H10" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="I10" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J10" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K10" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="L10" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M10" t="n">
         <v>11</v>
@@ -1779,25 +1779,25 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="R10" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="S10" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="T10" t="n">
-        <v>391</v>
+        <v>422</v>
       </c>
       <c r="U10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V10" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="W10" t="n">
         <v>12</v>
@@ -1806,22 +1806,22 @@
         <v>9</v>
       </c>
       <c r="Y10" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="Z10" t="n">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.706</v>
+        <v>0.715</v>
       </c>
       <c r="AB10" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AC10" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.554</v>
+        <v>0.541</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -1845,48 +1845,48 @@
         <v>5</v>
       </c>
       <c r="AL10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.333</v>
+        <v>0.294</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>640:40</t>
+          <t>682:20</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>288.72</v>
+        <v>310.92</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.639</v>
+        <v>0.645</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.668</v>
+        <v>0.671</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.146</v>
+        <v>1.151</v>
       </c>
       <c r="AS10" t="n">
         <v>0.142</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.602</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.805</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.206</v>
+        <v>0.208</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.075</v>
       </c>
       <c r="AX10" t="n">
         <v>0.127</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="11">
@@ -1896,64 +1896,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="D11" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E11" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F11" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G11" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="H11" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I11" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J11" t="n">
+        <v>21</v>
+      </c>
+      <c r="K11" t="n">
+        <v>95</v>
+      </c>
+      <c r="L11" t="n">
+        <v>27</v>
+      </c>
+      <c r="M11" t="n">
+        <v>21</v>
+      </c>
+      <c r="N11" t="n">
+        <v>10</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>42</v>
+      </c>
+      <c r="R11" t="n">
+        <v>75</v>
+      </c>
+      <c r="S11" t="n">
+        <v>58</v>
+      </c>
+      <c r="T11" t="n">
+        <v>289</v>
+      </c>
+      <c r="U11" t="n">
         <v>20</v>
-      </c>
-      <c r="K11" t="n">
-        <v>92</v>
-      </c>
-      <c r="L11" t="n">
-        <v>23</v>
-      </c>
-      <c r="M11" t="n">
-        <v>20</v>
-      </c>
-      <c r="N11" t="n">
-        <v>9</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>39</v>
-      </c>
-      <c r="R11" t="n">
-        <v>74</v>
-      </c>
-      <c r="S11" t="n">
-        <v>56</v>
-      </c>
-      <c r="T11" t="n">
-        <v>274</v>
-      </c>
-      <c r="U11" t="n">
-        <v>18</v>
       </c>
       <c r="V11" t="n">
         <v>18</v>
@@ -1965,84 +1965,84 @@
         <v>12</v>
       </c>
       <c r="Y11" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="Z11" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.757</v>
+        <v>0.752</v>
       </c>
       <c r="AB11" t="n">
         <v>15</v>
       </c>
       <c r="AC11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.417</v>
+        <v>0.405</v>
       </c>
       <c r="AE11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>31</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="AH11" t="n">
         <v>12</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AI11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AK11" t="n">
         <v>29</v>
       </c>
-      <c r="AG11" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>28</v>
-      </c>
       <c r="AL11" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.424</v>
+        <v>0.42</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>617:16</t>
+          <t>650:32</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>266.08</v>
+        <v>281.96</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.587</v>
+        <v>0.582</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.621</v>
+        <v>0.617</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.147</v>
+        <v>0.149</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.223</v>
+        <v>0.22</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.513</v>
+        <v>0.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.198</v>
+        <v>0.197</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.041</v>
+        <v>0.045</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.184</v>
+        <v>0.18</v>
       </c>
       <c r="AY11" t="n">
         <v>0.023</v>
@@ -2055,37 +2055,37 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="D12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="H12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J12" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="K12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M12" t="n">
         <v>26</v>
@@ -2097,25 +2097,25 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>25</v>
+      </c>
+      <c r="R12" t="n">
+        <v>85</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="n">
+        <v>161</v>
+      </c>
+      <c r="U12" t="n">
+        <v>32</v>
+      </c>
+      <c r="V12" t="n">
         <v>22</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>22</v>
-      </c>
-      <c r="R12" t="n">
-        <v>79</v>
-      </c>
-      <c r="S12" t="n">
-        <v>24</v>
-      </c>
-      <c r="T12" t="n">
-        <v>148</v>
-      </c>
-      <c r="U12" t="n">
-        <v>29</v>
-      </c>
-      <c r="V12" t="n">
-        <v>17</v>
       </c>
       <c r="W12" t="n">
         <v>7</v>
@@ -2124,87 +2124,87 @@
         <v>4</v>
       </c>
       <c r="Y12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Z12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.667</v>
+        <v>0.694</v>
       </c>
       <c r="AB12" t="n">
         <v>4</v>
       </c>
       <c r="AC12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.211</v>
+        <v>0.182</v>
       </c>
       <c r="AE12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.467</v>
+        <v>0.484</v>
       </c>
       <c r="AH12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.174</v>
+        <v>0.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AL12" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.356</v>
+        <v>0.347</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>556:36</t>
+          <t>604:06</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>212.76</v>
+        <v>235.08</v>
       </c>
       <c r="AP12" t="n">
         <v>0.449</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.477</v>
+        <v>0.478</v>
       </c>
       <c r="AR12" t="n">
         <v>0.855</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.103</v>
+        <v>0.106</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.124</v>
+        <v>0.128</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.636</v>
+        <v>2.64</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.175</v>
+        <v>0.177</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
       <c r="AX12" t="n">
         <v>0.098</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.064</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -2214,37 +2214,37 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C13" t="n">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E13" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H13" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I13" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J13" t="n">
         <v>18</v>
       </c>
       <c r="K13" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L13" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M13" t="n">
         <v>17</v>
@@ -2256,40 +2256,40 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R13" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="S13" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="T13" t="n">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="U13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V13" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="W13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="Z13" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.678</v>
+        <v>0.7</v>
       </c>
       <c r="AB13" t="n">
         <v>5</v>
@@ -2313,57 +2313,57 @@
         <v>8</v>
       </c>
       <c r="AI13" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.258</v>
+        <v>0.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AL13" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.289</v>
+        <v>0.3</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>496:18</t>
+          <t>540:30</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>142.84</v>
+        <v>156.92</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.465</v>
+        <v>0.484</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.497</v>
+        <v>0.518</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.2</v>
+        <v>0.224</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.5</v>
+        <v>1.385</v>
       </c>
       <c r="AV13" t="n">
         <v>0.132</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.053</v>
+        <v>0.056</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.157</v>
+        <v>0.16</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="14">
@@ -2373,22 +2373,22 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>32</v>
+      </c>
+      <c r="C14" t="n">
+        <v>177</v>
+      </c>
+      <c r="D14" t="n">
+        <v>24</v>
+      </c>
+      <c r="E14" t="n">
+        <v>43</v>
+      </c>
+      <c r="F14" t="n">
         <v>30</v>
       </c>
-      <c r="C14" t="n">
-        <v>172</v>
-      </c>
-      <c r="D14" t="n">
-        <v>23</v>
-      </c>
-      <c r="E14" t="n">
-        <v>41</v>
-      </c>
-      <c r="F14" t="n">
-        <v>29</v>
-      </c>
       <c r="G14" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H14" t="n">
         <v>39</v>
@@ -2397,16 +2397,16 @@
         <v>45</v>
       </c>
       <c r="J14" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="K14" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
@@ -2415,19 +2415,19 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Q14" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="R14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S14" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="T14" t="n">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="U14" t="n">
         <v>28</v>
@@ -2436,10 +2436,10 @@
         <v>14</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="n">
         <v>43</v>
@@ -2460,10 +2460,10 @@
         <v>0.636</v>
       </c>
       <c r="AE14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG14" t="n">
         <v>0.5</v>
@@ -2472,57 +2472,57 @@
         <v>9</v>
       </c>
       <c r="AI14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="AK14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL14" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.323</v>
+        <v>0.318</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>591:08</t>
+          <t>616:07</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>149.8</v>
+        <v>160.8</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.583</v>
+        <v>0.57</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.643</v>
+        <v>0.629</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.148</v>
+        <v>1.101</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.107</v>
+        <v>0.124</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.342</v>
+        <v>0.322</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.562</v>
+        <v>4.65</v>
       </c>
       <c r="AV14" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AX14" t="n">
         <v>0.116</v>
       </c>
-      <c r="AW14" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0.113</v>
-      </c>
       <c r="AY14" t="n">
-        <v>0.098</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="15">
@@ -2532,34 +2532,34 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F15" t="n">
         <v>12</v>
       </c>
       <c r="G15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H15" t="n">
+        <v>16</v>
+      </c>
+      <c r="I15" t="n">
+        <v>19</v>
+      </c>
+      <c r="J15" t="n">
         <v>15</v>
       </c>
-      <c r="I15" t="n">
-        <v>17</v>
-      </c>
-      <c r="J15" t="n">
-        <v>12</v>
-      </c>
       <c r="K15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2574,19 +2574,19 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S15" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="U15" t="n">
         <v>8</v>
@@ -2601,31 +2601,31 @@
         <v>4</v>
       </c>
       <c r="Y15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.85</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD15" t="n">
         <v>1</v>
       </c>
       <c r="AE15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="AH15" t="n">
         <v>2</v>
@@ -2640,36 +2640,36 @@
         <v>10</v>
       </c>
       <c r="AL15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.476</v>
+        <v>0.455</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>144:38</t>
+          <t>158:16</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>56.48</v>
+        <v>62.36</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.66</v>
+        <v>0.647</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.707</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.363</v>
+        <v>1.315</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.035</v>
+        <v>0.048</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.319</v>
+        <v>0.314</v>
       </c>
       <c r="AU15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV15" t="n">
         <v>0.179</v>
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.094</v>
+        <v>0.101</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="16">
@@ -2831,7 +2831,7 @@
         <v>1</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.217</v>
+        <v>0.215</v>
       </c>
       <c r="AW16" t="n">
         <v>0.02</v>
@@ -2850,64 +2850,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="D17" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E17" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I17" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J17" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K17" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L17" t="n">
         <v>13</v>
       </c>
       <c r="M17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R17" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="S17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T17" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="U17" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V17" t="n">
         <v>8</v>
@@ -2919,22 +2919,22 @@
         <v>10</v>
       </c>
       <c r="Y17" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z17" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AA17" t="n">
         <v>0.679</v>
       </c>
       <c r="AB17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC17" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.6</v>
+        <v>0.579</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -2949,57 +2949,57 @@
         <v>5</v>
       </c>
       <c r="AI17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL17" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.227</v>
+        <v>0.239</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>377:17</t>
+          <t>403:50</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>184.92</v>
+        <v>194.8</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="AQ17" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="AU17" t="n">
         <v>0.581</v>
       </c>
-      <c r="AR17" t="n">
-        <v>0.973</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0.162</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0.199</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AV17" t="n">
-        <v>0.225</v>
+        <v>0.22</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.038</v>
+        <v>0.035</v>
       </c>
       <c r="AX17" t="n">
         <v>0.128</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.017</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="18">
@@ -3149,7 +3149,7 @@
         <v>1.167</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.203</v>
+        <v>0.201</v>
       </c>
       <c r="AW18" t="n">
         <v>0.107</v>
@@ -3158,7 +3158,7 @@
         <v>0.239</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="19">
@@ -3168,43 +3168,43 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="E19" t="n">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H19" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I19" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="J19" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K19" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3216,19 +3216,19 @@
         <v>10</v>
       </c>
       <c r="R19" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="S19" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="T19" t="n">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="U19" t="n">
         <v>8</v>
       </c>
       <c r="V19" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="W19" t="n">
         <v>2</v>
@@ -3237,31 +3237,31 @@
         <v>2</v>
       </c>
       <c r="Y19" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="Z19" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.701</v>
+        <v>0.705</v>
       </c>
       <c r="AB19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC19" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.421</v>
+        <v>0.417</v>
       </c>
       <c r="AE19" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.5</v>
+        <v>0.541</v>
       </c>
       <c r="AH19" t="n">
         <v>0</v>
@@ -3276,48 +3276,48 @@
         <v>1</v>
       </c>
       <c r="AL19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>232:56</t>
+          <t>268:37</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>102.24</v>
+        <v>123.76</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.507</v>
+        <v>0.528</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.58</v>
+        <v>0.589</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.047</v>
+        <v>1.083</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.098</v>
+        <v>0.081</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.472</v>
+        <v>0.433</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.201</v>
+        <v>0.21</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.075</v>
+        <v>0.073</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.111</v>
+        <v>0.119</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="20">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.114</v>
+        <v>0.113</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.272</v>
+        <v>0.271</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
@@ -3626,7 +3626,7 @@
         <v>1.95</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.276</v>
+        <v>0.274</v>
       </c>
       <c r="AW21" t="n">
         <v>0.016</v>
@@ -3635,7 +3635,7 @@
         <v>0.109</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.09</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -3645,22 +3645,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C22" t="n">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E22" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F22" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G22" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H22" t="n">
         <v>9</v>
@@ -3672,16 +3672,16 @@
         <v>21</v>
       </c>
       <c r="K22" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L22" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3693,25 +3693,25 @@
         <v>19</v>
       </c>
       <c r="R22" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="S22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="T22" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="U22" t="n">
         <v>10</v>
       </c>
       <c r="V22" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="W22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="n">
         <v>19</v>
@@ -3723,10 +3723,10 @@
         <v>0.528</v>
       </c>
       <c r="AB22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AD22" t="n">
         <v>0.5</v>
@@ -3735,10 +3735,10 @@
         <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.222</v>
+        <v>0.167</v>
       </c>
       <c r="AH22" t="n">
         <v>7</v>
@@ -3750,51 +3750,51 @@
         <v>0.304</v>
       </c>
       <c r="AK22" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AL22" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.375</v>
+        <v>0.403</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>333:13</t>
+          <t>351:42</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>150.04</v>
+        <v>161.04</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.5</v>
+        <v>0.511</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.507</v>
+        <v>0.517</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.886</v>
+        <v>0.913</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.127</v>
+        <v>0.118</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.073</v>
+        <v>0.067</v>
       </c>
       <c r="AU22" t="n">
         <v>1.105</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.206</v>
+        <v>0.209</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.082</v>
+        <v>0.093</v>
       </c>
       <c r="AX22" t="n">
         <v>0.126</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.023</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="23">
@@ -3804,40 +3804,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C23" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E23" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J23" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L23" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N23" t="n">
         <v>2</v>
@@ -3846,19 +3846,19 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>17</v>
+      </c>
+      <c r="R23" t="n">
+        <v>18</v>
+      </c>
+      <c r="S23" t="n">
         <v>13</v>
       </c>
-      <c r="Q23" t="n">
-        <v>13</v>
-      </c>
-      <c r="R23" t="n">
-        <v>16</v>
-      </c>
-      <c r="S23" t="n">
-        <v>8</v>
-      </c>
       <c r="T23" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="U23" t="n">
         <v>3</v>
@@ -3867,34 +3867,34 @@
         <v>8</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Z23" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.889</v>
+        <v>0.875</v>
       </c>
       <c r="AB23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC23" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AF23" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="AG23" t="n">
         <v>0.333</v>
@@ -3912,48 +3912,48 @@
         <v>2</v>
       </c>
       <c r="AL23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.154</v>
+        <v>0.143</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>145:31</t>
+          <t>178:46</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>69.76000000000001</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.418</v>
+        <v>0.412</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.432</v>
+        <v>0.438</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.702</v>
+        <v>0.708</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.186</v>
+        <v>0.191</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.055</v>
+        <v>0.103</v>
       </c>
       <c r="AU23" t="n">
-        <v>1</v>
+        <v>1.059</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.22</v>
+        <v>0.227</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.06</v>
+        <v>0.073</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.127</v>
+        <v>0.173</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.014</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="24">
@@ -3963,40 +3963,40 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C24" t="n">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="D24" t="n">
+        <v>66</v>
+      </c>
+      <c r="E24" t="n">
+        <v>146</v>
+      </c>
+      <c r="F24" t="n">
         <v>61</v>
       </c>
-      <c r="E24" t="n">
-        <v>133</v>
-      </c>
-      <c r="F24" t="n">
-        <v>58</v>
-      </c>
       <c r="G24" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H24" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="I24" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J24" t="n">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="K24" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="L24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M24" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="N24" t="n">
         <v>12</v>
@@ -4005,22 +4005,22 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="Q24" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="R24" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="S24" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="T24" t="n">
-        <v>434</v>
+        <v>471</v>
       </c>
       <c r="U24" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="V24" t="n">
         <v>24</v>
@@ -4032,87 +4032,87 @@
         <v>17</v>
       </c>
       <c r="Y24" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="Z24" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AB24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AC24" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.311</v>
+        <v>0.314</v>
       </c>
       <c r="AE24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF24" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.308</v>
+        <v>0.304</v>
       </c>
       <c r="AH24" t="n">
         <v>3</v>
       </c>
       <c r="AI24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="AK24" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="AL24" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.404</v>
+        <v>0.414</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>713:28</t>
+          <t>757:43</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>357.88</v>
+        <v>383.4</v>
       </c>
       <c r="AP24" t="n">
         <v>0.538</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.578</v>
+        <v>0.58</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.998</v>
+        <v>0.999</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.137</v>
+        <v>0.138</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.222</v>
+        <v>0.232</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.98</v>
+        <v>3.038</v>
       </c>
       <c r="AV24" t="n">
         <v>0.23</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.081</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.173</v>
+        <v>0.178</v>
       </c>
     </row>
     <row r="25">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -4308,22 +4308,22 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L26" t="n">
+        <v>40</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
         <v>35</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>34</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4440,132 +4440,132 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C27" t="n">
-        <v>2788</v>
+        <v>2978</v>
       </c>
       <c r="D27" t="n">
-        <v>619</v>
+        <v>668</v>
       </c>
       <c r="E27" t="n">
-        <v>1142</v>
+        <v>1233</v>
       </c>
       <c r="F27" t="n">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="G27" t="n">
-        <v>961</v>
+        <v>1014</v>
       </c>
       <c r="H27" t="n">
-        <v>518</v>
+        <v>553</v>
       </c>
       <c r="I27" t="n">
-        <v>726</v>
+        <v>773</v>
       </c>
       <c r="J27" t="n">
-        <v>586</v>
+        <v>633</v>
       </c>
       <c r="K27" t="n">
-        <v>769</v>
+        <v>821</v>
       </c>
       <c r="L27" t="n">
-        <v>351</v>
+        <v>388</v>
       </c>
       <c r="M27" t="n">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="N27" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="Q27" t="n">
+        <v>386</v>
+      </c>
+      <c r="R27" t="n">
+        <v>812</v>
+      </c>
+      <c r="S27" t="n">
+        <v>766</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3330</v>
+      </c>
+      <c r="U27" t="n">
+        <v>363</v>
+      </c>
+      <c r="V27" t="n">
+        <v>326</v>
+      </c>
+      <c r="W27" t="n">
+        <v>175</v>
+      </c>
+      <c r="X27" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>897</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1236</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>192</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>411</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>132</v>
+      </c>
+      <c r="AF27" t="n">
         <v>359</v>
       </c>
-      <c r="R27" t="n">
-        <v>766</v>
-      </c>
-      <c r="S27" t="n">
-        <v>717</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3099</v>
-      </c>
-      <c r="U27" t="n">
-        <v>346</v>
-      </c>
-      <c r="V27" t="n">
-        <v>298</v>
-      </c>
-      <c r="W27" t="n">
-        <v>165</v>
-      </c>
-      <c r="X27" t="n">
-        <v>96</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>836</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1160</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0.721</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>182</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>380</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0.479</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>119</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>328</v>
-      </c>
       <c r="AG27" t="n">
-        <v>0.363</v>
+        <v>0.368</v>
       </c>
       <c r="AH27" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="AI27" t="n">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.397</v>
+        <v>0.394</v>
       </c>
       <c r="AK27" t="n">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="AL27" t="n">
-        <v>757</v>
+        <v>798</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>6450:00</t>
+          <t>6850:00</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>2815.44</v>
+        <v>3008.12</v>
       </c>
       <c r="AP27" t="n">
         <v>0.54</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.575</v>
+        <v>0.576</v>
       </c>
       <c r="AR27" t="n">
         <v>0.99</v>
@@ -4577,16 +4577,16 @@
         <v>0.246</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.491</v>
+        <v>1.504</v>
       </c>
       <c r="AV27" t="n">
         <v>0.2</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.059</v>
+        <v>0.062</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.147</v>
+        <v>0.148</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -4599,153 +4599,153 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C28" t="n">
-        <v>2781</v>
+        <v>2956</v>
       </c>
       <c r="D28" t="n">
-        <v>623</v>
+        <v>653</v>
       </c>
       <c r="E28" t="n">
-        <v>1099</v>
+        <v>1168</v>
       </c>
       <c r="F28" t="n">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="G28" t="n">
-        <v>833</v>
+        <v>880</v>
       </c>
       <c r="H28" t="n">
-        <v>632</v>
+        <v>672</v>
       </c>
       <c r="I28" t="n">
-        <v>819</v>
+        <v>870</v>
       </c>
       <c r="J28" t="n">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="K28" t="n">
-        <v>831</v>
+        <v>870</v>
       </c>
       <c r="L28" t="n">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="M28" t="n">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="N28" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="Q28" t="n">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="R28" t="n">
-        <v>722</v>
+        <v>771</v>
       </c>
       <c r="S28" t="n">
-        <v>764</v>
+        <v>811</v>
       </c>
       <c r="T28" t="n">
-        <v>3212</v>
+        <v>3390</v>
       </c>
       <c r="U28" t="n">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="V28" t="n">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="W28" t="n">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="X28" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="Y28" t="n">
-        <v>977</v>
+        <v>1030</v>
       </c>
       <c r="Z28" t="n">
-        <v>1271</v>
+        <v>1338</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="AB28" t="n">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="AC28" t="n">
-        <v>388</v>
+        <v>417</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.466</v>
+        <v>0.46</v>
       </c>
       <c r="AE28" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="AF28" t="n">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.375</v>
+        <v>0.364</v>
       </c>
       <c r="AH28" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AI28" t="n">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.432</v>
+        <v>0.434</v>
       </c>
       <c r="AK28" t="n">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="AL28" t="n">
-        <v>604</v>
+        <v>645</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.334</v>
+        <v>0.347</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>6450:00</t>
+          <t>6850:00</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>2708.36</v>
+        <v>2870.8</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.556</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.607</v>
+        <v>0.608</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.027</v>
+        <v>1.03</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.154</v>
+        <v>0.153</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.327</v>
+        <v>0.328</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.303</v>
+        <v>1.291</v>
       </c>
       <c r="AV28" t="n">
         <v>0.2</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.141</v>
+        <v>0.138</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
         <v>0.667</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.191</v>
+        <v>0.189</v>
       </c>
       <c r="AW30" t="n">
         <v>0.129</v>
@@ -4974,156 +4974,156 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C31" t="n">
-        <v>5.696</v>
+        <v>5.72</v>
       </c>
       <c r="D31" t="n">
-        <v>1.261</v>
+        <v>1.2</v>
       </c>
       <c r="E31" t="n">
-        <v>2.348</v>
+        <v>2.32</v>
       </c>
       <c r="F31" t="n">
-        <v>0.957</v>
+        <v>0.96</v>
       </c>
       <c r="G31" t="n">
-        <v>2.609</v>
+        <v>2.56</v>
       </c>
       <c r="H31" t="n">
-        <v>0.304</v>
+        <v>0.44</v>
       </c>
       <c r="I31" t="n">
-        <v>0.739</v>
+        <v>0.88</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="K31" t="n">
-        <v>0.652</v>
+        <v>0.6</v>
       </c>
       <c r="L31" t="n">
-        <v>0.609</v>
+        <v>0.68</v>
       </c>
       <c r="M31" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.52</v>
       </c>
       <c r="N31" t="n">
-        <v>0.609</v>
+        <v>0.6</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.696</v>
+        <v>0.76</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.696</v>
+        <v>0.76</v>
       </c>
       <c r="R31" t="n">
-        <v>1.739</v>
+        <v>1.88</v>
       </c>
       <c r="S31" t="n">
-        <v>0.783</v>
+        <v>0.8</v>
       </c>
       <c r="T31" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="U31" t="n">
-        <v>0.913</v>
+        <v>0.92</v>
       </c>
       <c r="V31" t="n">
-        <v>0.304</v>
+        <v>0.4</v>
       </c>
       <c r="W31" t="n">
-        <v>0.609</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="X31" t="n">
-        <v>0.304</v>
+        <v>0.28</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.043</v>
+        <v>1.16</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.739</v>
+        <v>1.84</v>
       </c>
       <c r="AA31" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AF31" t="n">
         <v>0.6</v>
       </c>
-      <c r="AB31" t="n">
-        <v>0.391</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0.5649999999999999</v>
-      </c>
       <c r="AG31" t="n">
-        <v>0.231</v>
+        <v>0.2</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.609</v>
+        <v>0.64</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.304</v>
+        <v>1.32</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.467</v>
+        <v>0.485</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.348</v>
+        <v>0.32</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.304</v>
+        <v>1.24</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.267</v>
+        <v>0.258</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>5.977</v>
+        <v>6.027</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.544</v>
+        <v>0.541</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.539</v>
+        <v>0.543</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.953</v>
+        <v>0.949</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.116</v>
+        <v>0.126</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.061</v>
+        <v>0.09</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.438</v>
+        <v>1.368</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.196</v>
+        <v>0.191</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.047</v>
+        <v>0.051</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.057</v>
+        <v>0.051</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.036</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="32">
@@ -5133,97 +5133,97 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C32" t="n">
-        <v>10.344</v>
+        <v>10.529</v>
       </c>
       <c r="D32" t="n">
-        <v>3.281</v>
+        <v>3.441</v>
       </c>
       <c r="E32" t="n">
-        <v>5.031</v>
+        <v>5.176</v>
       </c>
       <c r="F32" t="n">
-        <v>0.156</v>
+        <v>0.147</v>
       </c>
       <c r="G32" t="n">
-        <v>0.469</v>
+        <v>0.5</v>
       </c>
       <c r="H32" t="n">
-        <v>3.312</v>
+        <v>3.206</v>
       </c>
       <c r="I32" t="n">
-        <v>5.094</v>
+        <v>4.941</v>
       </c>
       <c r="J32" t="n">
-        <v>1.031</v>
+        <v>1.059</v>
       </c>
       <c r="K32" t="n">
-        <v>2.062</v>
+        <v>2.059</v>
       </c>
       <c r="L32" t="n">
-        <v>1.312</v>
+        <v>1.382</v>
       </c>
       <c r="M32" t="n">
-        <v>0.344</v>
+        <v>0.324</v>
       </c>
       <c r="N32" t="n">
-        <v>1.094</v>
+        <v>1.029</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.281</v>
+        <v>1.294</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.281</v>
+        <v>1.294</v>
       </c>
       <c r="R32" t="n">
-        <v>2.969</v>
+        <v>2.941</v>
       </c>
       <c r="S32" t="n">
-        <v>4.125</v>
+        <v>4.088</v>
       </c>
       <c r="T32" t="n">
-        <v>391</v>
+        <v>422</v>
       </c>
       <c r="U32" t="n">
         <v>1</v>
       </c>
       <c r="V32" t="n">
-        <v>1.688</v>
+        <v>1.882</v>
       </c>
       <c r="W32" t="n">
-        <v>0.375</v>
+        <v>0.353</v>
       </c>
       <c r="X32" t="n">
-        <v>0.281</v>
+        <v>0.265</v>
       </c>
       <c r="Y32" t="n">
-        <v>5.562</v>
+        <v>5.618</v>
       </c>
       <c r="Z32" t="n">
-        <v>7.875</v>
+        <v>7.853</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.706</v>
+        <v>0.715</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.969</v>
+        <v>0.971</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.75</v>
+        <v>1.794</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.554</v>
+        <v>0.541</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
       <c r="AG32" t="n">
         <v>0.125</v>
@@ -5238,51 +5238,51 @@
         <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.156</v>
+        <v>0.147</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.469</v>
+        <v>0.5</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.333</v>
+        <v>0.294</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>9.022</v>
+        <v>9.145</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.639</v>
+        <v>0.645</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.668</v>
+        <v>0.671</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.146</v>
+        <v>1.151</v>
       </c>
       <c r="AS32" t="n">
         <v>0.142</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.602</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AU32" t="n">
-        <v>0.805</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.206</v>
+        <v>0.208</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.075</v>
       </c>
       <c r="AX32" t="n">
         <v>0.127</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="33">
@@ -5292,156 +5292,156 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>9.4</v>
+        <v>9.25</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>1.969</v>
       </c>
       <c r="E33" t="n">
-        <v>3.7</v>
+        <v>3.688</v>
       </c>
       <c r="F33" t="n">
-        <v>1.3</v>
+        <v>1.281</v>
       </c>
       <c r="G33" t="n">
-        <v>3.033</v>
+        <v>3</v>
       </c>
       <c r="H33" t="n">
-        <v>1.5</v>
+        <v>1.469</v>
       </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>1.844</v>
       </c>
       <c r="J33" t="n">
-        <v>0.667</v>
+        <v>0.656</v>
       </c>
       <c r="K33" t="n">
-        <v>3.067</v>
+        <v>2.969</v>
       </c>
       <c r="L33" t="n">
-        <v>0.767</v>
+        <v>0.844</v>
       </c>
       <c r="M33" t="n">
-        <v>0.667</v>
+        <v>0.656</v>
       </c>
       <c r="N33" t="n">
-        <v>0.3</v>
+        <v>0.312</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.3</v>
+        <v>1.312</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.3</v>
+        <v>1.312</v>
       </c>
       <c r="R33" t="n">
-        <v>2.467</v>
+        <v>2.344</v>
       </c>
       <c r="S33" t="n">
-        <v>1.867</v>
+        <v>1.812</v>
       </c>
       <c r="T33" t="n">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="U33" t="n">
-        <v>0.6</v>
+        <v>0.625</v>
       </c>
       <c r="V33" t="n">
-        <v>0.6</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="W33" t="n">
-        <v>0.733</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="X33" t="n">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.6</v>
+        <v>2.562</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.433</v>
+        <v>3.406</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.757</v>
+        <v>0.752</v>
       </c>
       <c r="AB33" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>2.156</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>20:19</t>
+        </is>
+      </c>
+      <c r="AO33" t="n">
+        <v>8.811</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AU33" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0.967</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>0.9330000000000001</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0.424</v>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>20:34</t>
-        </is>
-      </c>
-      <c r="AO33" t="n">
-        <v>8.869</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0.587</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0.621</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0.223</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0.513</v>
-      </c>
       <c r="AV33" t="n">
-        <v>0.198</v>
+        <v>0.197</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.041</v>
+        <v>0.045</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.184</v>
+        <v>0.18</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="34">
@@ -5451,156 +5451,156 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C34" t="n">
-        <v>6.276</v>
+        <v>6.484</v>
       </c>
       <c r="D34" t="n">
-        <v>0.897</v>
+        <v>0.903</v>
       </c>
       <c r="E34" t="n">
-        <v>2.241</v>
+        <v>2.258</v>
       </c>
       <c r="F34" t="n">
-        <v>1.241</v>
+        <v>1.29</v>
       </c>
       <c r="G34" t="n">
-        <v>3.897</v>
+        <v>4.065</v>
       </c>
       <c r="H34" t="n">
-        <v>0.759</v>
+        <v>0.806</v>
       </c>
       <c r="I34" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.129</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.548</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.742</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="T34" t="n">
+        <v>161</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.097</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.581</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="AF34" t="n">
         <v>1</v>
       </c>
-      <c r="J34" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1.517</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0.897</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.897</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0.759</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0.759</v>
-      </c>
-      <c r="R34" t="n">
-        <v>2.724</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0.828</v>
-      </c>
-      <c r="T34" t="n">
-        <v>148</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0.241</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.034</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.552</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0.211</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0.483</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.034</v>
-      </c>
       <c r="AG34" t="n">
-        <v>0.467</v>
+        <v>0.484</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.138</v>
+        <v>0.161</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.793</v>
+        <v>0.806</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.174</v>
+        <v>0.2</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.103</v>
+        <v>1.129</v>
       </c>
       <c r="AL34" t="n">
-        <v>3.103</v>
+        <v>3.258</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.356</v>
+        <v>0.347</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>7.337</v>
+        <v>7.583</v>
       </c>
       <c r="AP34" t="n">
         <v>0.449</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.477</v>
+        <v>0.478</v>
       </c>
       <c r="AR34" t="n">
         <v>0.855</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.103</v>
+        <v>0.106</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.124</v>
+        <v>0.128</v>
       </c>
       <c r="AU34" t="n">
-        <v>2.636</v>
+        <v>2.64</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.175</v>
+        <v>0.177</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
       <c r="AX34" t="n">
         <v>0.098</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="35">
@@ -5610,88 +5610,88 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C35" t="n">
-        <v>4.194</v>
+        <v>4.515</v>
       </c>
       <c r="D35" t="n">
-        <v>0.71</v>
+        <v>0.788</v>
       </c>
       <c r="E35" t="n">
-        <v>1.258</v>
+        <v>1.303</v>
       </c>
       <c r="F35" t="n">
-        <v>0.677</v>
+        <v>0.697</v>
       </c>
       <c r="G35" t="n">
-        <v>2.452</v>
+        <v>2.485</v>
       </c>
       <c r="H35" t="n">
-        <v>0.742</v>
+        <v>0.848</v>
       </c>
       <c r="I35" t="n">
-        <v>1.161</v>
+        <v>1.303</v>
       </c>
       <c r="J35" t="n">
-        <v>0.581</v>
+        <v>0.545</v>
       </c>
       <c r="K35" t="n">
-        <v>2.032</v>
+        <v>2.121</v>
       </c>
       <c r="L35" t="n">
-        <v>0.774</v>
+        <v>0.848</v>
       </c>
       <c r="M35" t="n">
-        <v>0.548</v>
+        <v>0.515</v>
       </c>
       <c r="N35" t="n">
-        <v>0.194</v>
+        <v>0.182</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.387</v>
+        <v>0.394</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.387</v>
+        <v>0.394</v>
       </c>
       <c r="R35" t="n">
-        <v>1.226</v>
+        <v>1.273</v>
       </c>
       <c r="S35" t="n">
-        <v>1.161</v>
+        <v>1.273</v>
       </c>
       <c r="T35" t="n">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="U35" t="n">
-        <v>0.29</v>
+        <v>0.333</v>
       </c>
       <c r="V35" t="n">
-        <v>1.032</v>
+        <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>0.29</v>
+        <v>0.333</v>
       </c>
       <c r="X35" t="n">
-        <v>0.129</v>
+        <v>0.152</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.29</v>
+        <v>1.485</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.903</v>
+        <v>2.121</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.678</v>
+        <v>0.7</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.161</v>
+        <v>0.152</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.387</v>
+        <v>0.364</v>
       </c>
       <c r="AD35" t="n">
         <v>0.417</v>
@@ -5700,66 +5700,66 @@
         <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.129</v>
+        <v>0.121</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.258</v>
+        <v>0.242</v>
       </c>
       <c r="AI35" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.258</v>
+        <v>0.25</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.419</v>
+        <v>0.455</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.452</v>
+        <v>1.515</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.289</v>
+        <v>0.3</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>4.608</v>
+        <v>4.755</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.465</v>
+        <v>0.484</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.497</v>
+        <v>0.518</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.2</v>
+        <v>0.224</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.5</v>
+        <v>1.385</v>
       </c>
       <c r="AV35" t="n">
         <v>0.132</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.053</v>
+        <v>0.056</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.157</v>
+        <v>0.16</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="36">
@@ -5769,156 +5769,156 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C36" t="n">
-        <v>5.733</v>
+        <v>5.531</v>
       </c>
       <c r="D36" t="n">
-        <v>0.767</v>
+        <v>0.75</v>
       </c>
       <c r="E36" t="n">
-        <v>1.367</v>
+        <v>1.344</v>
       </c>
       <c r="F36" t="n">
-        <v>0.967</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>2.433</v>
+        <v>2.438</v>
       </c>
       <c r="H36" t="n">
-        <v>1.3</v>
+        <v>1.219</v>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>1.406</v>
       </c>
       <c r="J36" t="n">
-        <v>2.967</v>
+        <v>2.906</v>
       </c>
       <c r="K36" t="n">
-        <v>1.8</v>
+        <v>1.812</v>
       </c>
       <c r="L36" t="n">
-        <v>0.6</v>
+        <v>0.594</v>
       </c>
       <c r="M36" t="n">
-        <v>0.667</v>
+        <v>0.656</v>
       </c>
       <c r="N36" t="n">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.533</v>
+        <v>0.625</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.533</v>
+        <v>0.625</v>
       </c>
       <c r="R36" t="n">
-        <v>1.533</v>
+        <v>1.469</v>
       </c>
       <c r="S36" t="n">
-        <v>2.067</v>
+        <v>2</v>
       </c>
       <c r="T36" t="n">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="U36" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.875</v>
       </c>
       <c r="V36" t="n">
-        <v>0.467</v>
+        <v>0.438</v>
       </c>
       <c r="W36" t="n">
-        <v>0.067</v>
+        <v>0.156</v>
       </c>
       <c r="X36" t="n">
-        <v>0.067</v>
+        <v>0.094</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.433</v>
+        <v>1.344</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.7</v>
+        <v>1.594</v>
       </c>
       <c r="AA36" t="n">
         <v>0.843</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.233</v>
+        <v>0.219</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.367</v>
+        <v>0.344</v>
       </c>
       <c r="AD36" t="n">
         <v>0.636</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.4</v>
+        <v>0.406</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.8</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AG36" t="n">
         <v>0.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.3</v>
+        <v>0.281</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.367</v>
+        <v>0.375</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.667</v>
+        <v>0.656</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.067</v>
+        <v>2.062</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.323</v>
+        <v>0.318</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>4.993</v>
+        <v>5.025</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.583</v>
+        <v>0.57</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.643</v>
+        <v>0.629</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.148</v>
+        <v>1.101</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.107</v>
+        <v>0.124</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.342</v>
+        <v>0.322</v>
       </c>
       <c r="AU36" t="n">
-        <v>5.562</v>
+        <v>4.65</v>
       </c>
       <c r="AV36" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AX36" t="n">
         <v>0.116</v>
       </c>
-      <c r="AW36" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>0.113</v>
-      </c>
       <c r="AY36" t="n">
-        <v>0.105</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="37">
@@ -5928,144 +5928,144 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C37" t="n">
-        <v>5.923</v>
+        <v>5.467</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>1.615</v>
+        <v>1.6</v>
       </c>
       <c r="F37" t="n">
-        <v>0.923</v>
+        <v>0.8</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H37" t="n">
-        <v>1.154</v>
+        <v>1.067</v>
       </c>
       <c r="I37" t="n">
-        <v>1.308</v>
+        <v>1.267</v>
       </c>
       <c r="J37" t="n">
-        <v>0.923</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>0.846</v>
+        <v>0.867</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.154</v>
+        <v>0.133</v>
       </c>
       <c r="N37" t="n">
-        <v>0.077</v>
+        <v>0.067</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.154</v>
+        <v>0.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.154</v>
+        <v>0.2</v>
       </c>
       <c r="R37" t="n">
-        <v>0.846</v>
+        <v>0.8</v>
       </c>
       <c r="S37" t="n">
-        <v>1.077</v>
+        <v>1.133</v>
       </c>
       <c r="T37" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="U37" t="n">
-        <v>0.615</v>
+        <v>0.533</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0.615</v>
+        <v>0.533</v>
       </c>
       <c r="X37" t="n">
-        <v>0.308</v>
+        <v>0.267</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.308</v>
+        <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.538</v>
+        <v>1.467</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.85</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.154</v>
+        <v>0.2</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.154</v>
+        <v>0.2</v>
       </c>
       <c r="AD37" t="n">
         <v>1</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.231</v>
+        <v>1.2</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.154</v>
+        <v>0.133</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.385</v>
+        <v>0.333</v>
       </c>
       <c r="AJ37" t="n">
         <v>0.4</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.769</v>
+        <v>0.667</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.615</v>
+        <v>1.467</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.476</v>
+        <v>0.455</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>4.345</v>
+        <v>4.157</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.66</v>
+        <v>0.647</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.707</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.363</v>
+        <v>1.315</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.035</v>
+        <v>0.048</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.319</v>
+        <v>0.314</v>
       </c>
       <c r="AU37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV37" t="n">
         <v>0.179</v>
@@ -6074,10 +6074,10 @@
         <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.094</v>
+        <v>0.101</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.033</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="38">
@@ -6227,7 +6227,7 @@
         <v>1</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.217</v>
+        <v>0.215</v>
       </c>
       <c r="AW38" t="n">
         <v>0.02</v>
@@ -6246,156 +6246,156 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C39" t="n">
-        <v>8.571</v>
+        <v>8.173999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>2.571</v>
+        <v>2.435</v>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>3.826</v>
       </c>
       <c r="F39" t="n">
-        <v>0.714</v>
+        <v>0.696</v>
       </c>
       <c r="G39" t="n">
-        <v>2.476</v>
+        <v>2.435</v>
       </c>
       <c r="H39" t="n">
-        <v>1.286</v>
+        <v>1.217</v>
       </c>
       <c r="I39" t="n">
-        <v>2.048</v>
+        <v>1.957</v>
       </c>
       <c r="J39" t="n">
-        <v>0.714</v>
+        <v>0.783</v>
       </c>
       <c r="K39" t="n">
-        <v>1.857</v>
+        <v>1.826</v>
       </c>
       <c r="L39" t="n">
-        <v>0.619</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.783</v>
       </c>
       <c r="N39" t="n">
-        <v>0.286</v>
+        <v>0.304</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.429</v>
+        <v>1.348</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.429</v>
+        <v>1.348</v>
       </c>
       <c r="R39" t="n">
-        <v>1.524</v>
+        <v>1.522</v>
       </c>
       <c r="S39" t="n">
-        <v>1.524</v>
+        <v>1.478</v>
       </c>
       <c r="T39" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="U39" t="n">
-        <v>1.619</v>
+        <v>1.565</v>
       </c>
       <c r="V39" t="n">
-        <v>0.381</v>
+        <v>0.348</v>
       </c>
       <c r="W39" t="n">
-        <v>0.857</v>
+        <v>0.783</v>
       </c>
       <c r="X39" t="n">
-        <v>0.476</v>
+        <v>0.435</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.619</v>
+        <v>2.478</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.857</v>
+        <v>3.652</v>
       </c>
       <c r="AA39" t="n">
         <v>0.679</v>
       </c>
       <c r="AB39" t="n">
-        <v>1</v>
+        <v>0.957</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.667</v>
+        <v>1.652</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.6</v>
+        <v>0.579</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.238</v>
+        <v>0.217</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.524</v>
+        <v>0.478</v>
       </c>
       <c r="AG39" t="n">
         <v>0.455</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.238</v>
+        <v>0.217</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.381</v>
+        <v>0.435</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.476</v>
+        <v>0.478</v>
       </c>
       <c r="AL39" t="n">
-        <v>2.095</v>
+        <v>2</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.227</v>
+        <v>0.239</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>8.805999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="AQ39" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="AU39" t="n">
         <v>0.581</v>
       </c>
-      <c r="AR39" t="n">
-        <v>0.973</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>0.162</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0.199</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AV39" t="n">
-        <v>0.225</v>
+        <v>0.22</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.038</v>
+        <v>0.035</v>
       </c>
       <c r="AX39" t="n">
         <v>0.128</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.027</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="40">
@@ -6545,7 +6545,7 @@
         <v>1.167</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.203</v>
+        <v>0.201</v>
       </c>
       <c r="AW40" t="n">
         <v>0.107</v>
@@ -6564,100 +6564,100 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C41" t="n">
-        <v>5.632</v>
+        <v>6.381</v>
       </c>
       <c r="D41" t="n">
-        <v>1.842</v>
+        <v>2.19</v>
       </c>
       <c r="E41" t="n">
-        <v>3.579</v>
+        <v>4.048</v>
       </c>
       <c r="F41" t="n">
-        <v>0.053</v>
+        <v>0.048</v>
       </c>
       <c r="G41" t="n">
-        <v>0.211</v>
+        <v>0.238</v>
       </c>
       <c r="H41" t="n">
-        <v>1.789</v>
+        <v>1.857</v>
       </c>
       <c r="I41" t="n">
-        <v>2.421</v>
+        <v>2.571</v>
       </c>
       <c r="J41" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.714</v>
       </c>
       <c r="K41" t="n">
-        <v>1.105</v>
+        <v>1.238</v>
       </c>
       <c r="L41" t="n">
-        <v>0.842</v>
+        <v>0.857</v>
       </c>
       <c r="M41" t="n">
-        <v>0.316</v>
+        <v>0.381</v>
       </c>
       <c r="N41" t="n">
-        <v>0.263</v>
+        <v>0.333</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.526</v>
+        <v>0.476</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.526</v>
+        <v>0.476</v>
       </c>
       <c r="R41" t="n">
-        <v>2.368</v>
+        <v>2.286</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>2.286</v>
       </c>
       <c r="T41" t="n">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="U41" t="n">
-        <v>0.421</v>
+        <v>0.381</v>
       </c>
       <c r="V41" t="n">
-        <v>1.263</v>
+        <v>1.429</v>
       </c>
       <c r="W41" t="n">
-        <v>0.105</v>
+        <v>0.095</v>
       </c>
       <c r="X41" t="n">
-        <v>0.105</v>
+        <v>0.095</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.474</v>
+        <v>2.619</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.526</v>
+        <v>3.714</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.701</v>
+        <v>0.705</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.421</v>
+        <v>0.476</v>
       </c>
       <c r="AC41" t="n">
-        <v>1</v>
+        <v>1.143</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.421</v>
+        <v>0.417</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.737</v>
+        <v>0.952</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.474</v>
+        <v>1.762</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.5</v>
+        <v>0.541</v>
       </c>
       <c r="AH41" t="n">
         <v>0</v>
@@ -6669,51 +6669,51 @@
         <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.053</v>
+        <v>0.048</v>
       </c>
       <c r="AL41" t="n">
-        <v>0.211</v>
+        <v>0.238</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>5.381</v>
+        <v>5.893</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.507</v>
+        <v>0.528</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.58</v>
+        <v>0.589</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.047</v>
+        <v>1.083</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.098</v>
+        <v>0.081</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.472</v>
+        <v>0.433</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.201</v>
+        <v>0.21</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.075</v>
+        <v>0.073</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.111</v>
+        <v>0.119</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="42">
@@ -6863,10 +6863,10 @@
         <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.114</v>
+        <v>0.113</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.272</v>
+        <v>0.271</v>
       </c>
       <c r="AX42" t="n">
         <v>0</v>
@@ -7022,7 +7022,7 @@
         <v>1.95</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.276</v>
+        <v>0.274</v>
       </c>
       <c r="AW43" t="n">
         <v>0.016</v>
@@ -7031,7 +7031,7 @@
         <v>0.109</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.109</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="44">
@@ -7041,156 +7041,156 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C44" t="n">
-        <v>5.542</v>
+        <v>5.654</v>
       </c>
       <c r="D44" t="n">
-        <v>0.833</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>1.875</v>
+        <v>1.923</v>
       </c>
       <c r="F44" t="n">
-        <v>1.167</v>
+        <v>1.231</v>
       </c>
       <c r="G44" t="n">
-        <v>3.292</v>
+        <v>3.269</v>
       </c>
       <c r="H44" t="n">
-        <v>0.375</v>
+        <v>0.346</v>
       </c>
       <c r="I44" t="n">
-        <v>0.667</v>
+        <v>0.615</v>
       </c>
       <c r="J44" t="n">
-        <v>0.875</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>1.417</v>
+        <v>1.385</v>
       </c>
       <c r="L44" t="n">
-        <v>1.042</v>
+        <v>1.154</v>
       </c>
       <c r="M44" t="n">
-        <v>0.625</v>
+        <v>0.615</v>
       </c>
       <c r="N44" t="n">
-        <v>0.375</v>
+        <v>0.385</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0.792</v>
+        <v>0.731</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.792</v>
+        <v>0.731</v>
       </c>
       <c r="R44" t="n">
-        <v>2</v>
+        <v>2.038</v>
       </c>
       <c r="S44" t="n">
-        <v>0.958</v>
+        <v>0.962</v>
       </c>
       <c r="T44" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="U44" t="n">
-        <v>0.417</v>
+        <v>0.385</v>
       </c>
       <c r="V44" t="n">
-        <v>0.625</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="W44" t="n">
-        <v>0.25</v>
+        <v>0.346</v>
       </c>
       <c r="X44" t="n">
-        <v>0.125</v>
+        <v>0.154</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.792</v>
+        <v>0.731</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.5</v>
+        <v>1.385</v>
       </c>
       <c r="AA44" t="n">
         <v>0.528</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.333</v>
+        <v>0.346</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.667</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AD44" t="n">
         <v>0.5</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.083</v>
+        <v>0.077</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.375</v>
+        <v>0.462</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.222</v>
+        <v>0.167</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.292</v>
+        <v>0.269</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.958</v>
+        <v>0.885</v>
       </c>
       <c r="AJ44" t="n">
         <v>0.304</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.875</v>
+        <v>0.962</v>
       </c>
       <c r="AL44" t="n">
-        <v>2.333</v>
+        <v>2.385</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.375</v>
+        <v>0.403</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>6.252</v>
+        <v>6.194</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.5</v>
+        <v>0.511</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.507</v>
+        <v>0.517</v>
       </c>
       <c r="AR44" t="n">
-        <v>0.886</v>
+        <v>0.913</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.127</v>
+        <v>0.118</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.073</v>
+        <v>0.067</v>
       </c>
       <c r="AU44" t="n">
         <v>1.105</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.206</v>
+        <v>0.209</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.082</v>
+        <v>0.093</v>
       </c>
       <c r="AX44" t="n">
         <v>0.126</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="45">
@@ -7200,91 +7200,91 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C45" t="n">
-        <v>5.444</v>
+        <v>5.727</v>
       </c>
       <c r="D45" t="n">
-        <v>2.222</v>
+        <v>2.273</v>
       </c>
       <c r="E45" t="n">
-        <v>4.667</v>
+        <v>4.909</v>
       </c>
       <c r="F45" t="n">
-        <v>0.222</v>
+        <v>0.182</v>
       </c>
       <c r="G45" t="n">
-        <v>1.444</v>
+        <v>1.273</v>
       </c>
       <c r="H45" t="n">
-        <v>0.333</v>
+        <v>0.636</v>
       </c>
       <c r="I45" t="n">
-        <v>0.444</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>1.444</v>
+        <v>1.636</v>
       </c>
       <c r="K45" t="n">
-        <v>1.667</v>
+        <v>2.273</v>
       </c>
       <c r="L45" t="n">
-        <v>0.889</v>
+        <v>1.091</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="N45" t="n">
-        <v>0.222</v>
+        <v>0.182</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.444</v>
+        <v>1.545</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.444</v>
+        <v>1.545</v>
       </c>
       <c r="R45" t="n">
-        <v>1.778</v>
+        <v>1.636</v>
       </c>
       <c r="S45" t="n">
-        <v>0.889</v>
+        <v>1.182</v>
       </c>
       <c r="T45" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="U45" t="n">
-        <v>0.333</v>
+        <v>0.273</v>
       </c>
       <c r="V45" t="n">
-        <v>0.889</v>
+        <v>0.727</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.889</v>
+        <v>1.273</v>
       </c>
       <c r="Z45" t="n">
-        <v>1</v>
+        <v>1.455</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.889</v>
+        <v>0.875</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.667</v>
+        <v>0.636</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.111</v>
+        <v>1.273</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -7305,51 +7305,51 @@
         <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.222</v>
+        <v>0.182</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.444</v>
+        <v>1.273</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.154</v>
+        <v>0.143</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>7.751</v>
+        <v>8.087</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.418</v>
+        <v>0.412</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.432</v>
+        <v>0.438</v>
       </c>
       <c r="AR45" t="n">
-        <v>0.702</v>
+        <v>0.708</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.186</v>
+        <v>0.191</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.055</v>
+        <v>0.103</v>
       </c>
       <c r="AU45" t="n">
-        <v>1</v>
+        <v>1.059</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.22</v>
+        <v>0.227</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.06</v>
+        <v>0.073</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.127</v>
+        <v>0.173</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.052</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="46">
@@ -7359,118 +7359,118 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C46" t="n">
-        <v>11.156</v>
+        <v>11.265</v>
       </c>
       <c r="D46" t="n">
-        <v>1.906</v>
+        <v>1.941</v>
       </c>
       <c r="E46" t="n">
-        <v>4.156</v>
+        <v>4.294</v>
       </c>
       <c r="F46" t="n">
-        <v>1.812</v>
+        <v>1.794</v>
       </c>
       <c r="G46" t="n">
-        <v>4.438</v>
+        <v>4.324</v>
       </c>
       <c r="H46" t="n">
-        <v>1.906</v>
+        <v>2</v>
       </c>
       <c r="I46" t="n">
-        <v>2.406</v>
+        <v>2.5</v>
       </c>
       <c r="J46" t="n">
-        <v>4.562</v>
+        <v>4.735</v>
       </c>
       <c r="K46" t="n">
-        <v>1.469</v>
+        <v>1.559</v>
       </c>
       <c r="L46" t="n">
-        <v>0.375</v>
+        <v>0.412</v>
       </c>
       <c r="M46" t="n">
-        <v>1.531</v>
+        <v>1.559</v>
       </c>
       <c r="N46" t="n">
-        <v>0.375</v>
+        <v>0.353</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.531</v>
+        <v>1.559</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.531</v>
+        <v>1.559</v>
       </c>
       <c r="R46" t="n">
-        <v>2.312</v>
+        <v>2.412</v>
       </c>
       <c r="S46" t="n">
-        <v>3.312</v>
+        <v>3.324</v>
       </c>
       <c r="T46" t="n">
-        <v>434</v>
+        <v>471</v>
       </c>
       <c r="U46" t="n">
-        <v>1.375</v>
+        <v>1.412</v>
       </c>
       <c r="V46" t="n">
-        <v>0.75</v>
+        <v>0.706</v>
       </c>
       <c r="W46" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.882</v>
       </c>
       <c r="X46" t="n">
-        <v>0.531</v>
+        <v>0.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.875</v>
+        <v>2.971</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.531</v>
+        <v>3.647</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.438</v>
+        <v>0.471</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.406</v>
+        <v>1.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.311</v>
+        <v>0.314</v>
       </c>
       <c r="AE46" t="n">
         <v>0.5</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.625</v>
+        <v>1.647</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.308</v>
+        <v>0.304</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.188</v>
+        <v>0.206</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.719</v>
+        <v>1.706</v>
       </c>
       <c r="AL46" t="n">
-        <v>4.25</v>
+        <v>4.118</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.404</v>
+        <v>0.414</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
@@ -7478,37 +7478,37 @@
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>11.184</v>
+        <v>11.276</v>
       </c>
       <c r="AP46" t="n">
         <v>0.538</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.578</v>
+        <v>0.58</v>
       </c>
       <c r="AR46" t="n">
-        <v>0.998</v>
+        <v>0.999</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.137</v>
+        <v>0.138</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.222</v>
+        <v>0.232</v>
       </c>
       <c r="AU46" t="n">
-        <v>2.98</v>
+        <v>3.038</v>
       </c>
       <c r="AV46" t="n">
         <v>0.23</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.081</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.173</v>
+        <v>0.178</v>
       </c>
     </row>
     <row r="47">
@@ -7677,7 +7677,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -7704,10 +7704,10 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1.75</v>
+        <v>1.706</v>
       </c>
       <c r="L48" t="n">
-        <v>1.094</v>
+        <v>1.176</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -7719,13 +7719,13 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1.062</v>
+        <v>1.029</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>0.156</v>
+        <v>0.147</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -7836,132 +7836,132 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C49" t="n">
-        <v>87.125</v>
+        <v>87.58799999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>19.344</v>
+        <v>19.647</v>
       </c>
       <c r="E49" t="n">
-        <v>35.688</v>
+        <v>36.265</v>
       </c>
       <c r="F49" t="n">
-        <v>10.75</v>
+        <v>10.676</v>
       </c>
       <c r="G49" t="n">
-        <v>30.031</v>
+        <v>29.824</v>
       </c>
       <c r="H49" t="n">
-        <v>16.188</v>
+        <v>16.265</v>
       </c>
       <c r="I49" t="n">
-        <v>22.688</v>
+        <v>22.735</v>
       </c>
       <c r="J49" t="n">
-        <v>18.312</v>
+        <v>18.618</v>
       </c>
       <c r="K49" t="n">
-        <v>24.031</v>
+        <v>24.147</v>
       </c>
       <c r="L49" t="n">
-        <v>10.969</v>
+        <v>11.412</v>
       </c>
       <c r="M49" t="n">
-        <v>7.562</v>
+        <v>7.471</v>
       </c>
       <c r="N49" t="n">
-        <v>4.781</v>
+        <v>4.676</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>12.281</v>
+        <v>12.382</v>
       </c>
       <c r="Q49" t="n">
-        <v>11.219</v>
+        <v>11.353</v>
       </c>
       <c r="R49" t="n">
-        <v>23.938</v>
+        <v>23.882</v>
       </c>
       <c r="S49" t="n">
-        <v>22.406</v>
+        <v>22.529</v>
       </c>
       <c r="T49" t="n">
-        <v>3099</v>
+        <v>3330</v>
       </c>
       <c r="U49" t="n">
-        <v>10.812</v>
+        <v>10.676</v>
       </c>
       <c r="V49" t="n">
-        <v>9.311999999999999</v>
+        <v>9.587999999999999</v>
       </c>
       <c r="W49" t="n">
-        <v>5.156</v>
+        <v>5.147</v>
       </c>
       <c r="X49" t="n">
-        <v>3</v>
+        <v>2.941</v>
       </c>
       <c r="Y49" t="n">
-        <v>26.125</v>
+        <v>26.382</v>
       </c>
       <c r="Z49" t="n">
-        <v>36.25</v>
+        <v>36.353</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.721</v>
+        <v>0.726</v>
       </c>
       <c r="AB49" t="n">
-        <v>5.688</v>
+        <v>5.647</v>
       </c>
       <c r="AC49" t="n">
-        <v>11.875</v>
+        <v>12.088</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.479</v>
+        <v>0.467</v>
       </c>
       <c r="AE49" t="n">
-        <v>3.719</v>
+        <v>3.882</v>
       </c>
       <c r="AF49" t="n">
-        <v>10.25</v>
+        <v>10.559</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.363</v>
+        <v>0.368</v>
       </c>
       <c r="AH49" t="n">
-        <v>2.531</v>
+        <v>2.5</v>
       </c>
       <c r="AI49" t="n">
-        <v>6.375</v>
+        <v>6.353</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.397</v>
+        <v>0.394</v>
       </c>
       <c r="AK49" t="n">
-        <v>8.218999999999999</v>
+        <v>8.176</v>
       </c>
       <c r="AL49" t="n">
-        <v>23.656</v>
+        <v>23.471</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>201:33</t>
+          <t>201:28</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>87.983</v>
+        <v>88.474</v>
       </c>
       <c r="AP49" t="n">
         <v>0.54</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.575</v>
+        <v>0.576</v>
       </c>
       <c r="AR49" t="n">
         <v>0.99</v>
@@ -7973,16 +7973,16 @@
         <v>0.246</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.491</v>
+        <v>1.504</v>
       </c>
       <c r="AV49" t="n">
         <v>0.2</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.059</v>
+        <v>0.062</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.147</v>
+        <v>0.148</v>
       </c>
       <c r="AY49" t="n">
         <v>0</v>
@@ -7995,153 +7995,153 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C50" t="n">
-        <v>86.90600000000001</v>
+        <v>86.941</v>
       </c>
       <c r="D50" t="n">
-        <v>19.469</v>
+        <v>19.206</v>
       </c>
       <c r="E50" t="n">
-        <v>34.344</v>
+        <v>34.353</v>
       </c>
       <c r="F50" t="n">
-        <v>9.406000000000001</v>
+        <v>9.587999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>26.031</v>
+        <v>25.882</v>
       </c>
       <c r="H50" t="n">
-        <v>19.75</v>
+        <v>19.765</v>
       </c>
       <c r="I50" t="n">
-        <v>25.594</v>
+        <v>25.588</v>
       </c>
       <c r="J50" t="n">
-        <v>16.938</v>
+        <v>16.706</v>
       </c>
       <c r="K50" t="n">
-        <v>25.969</v>
+        <v>25.588</v>
       </c>
       <c r="L50" t="n">
-        <v>8.625</v>
+        <v>8.5</v>
       </c>
       <c r="M50" t="n">
-        <v>6.094</v>
+        <v>6.206</v>
       </c>
       <c r="N50" t="n">
-        <v>4.875</v>
+        <v>4.794</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>13</v>
+        <v>12.941</v>
       </c>
       <c r="Q50" t="n">
-        <v>12.375</v>
+        <v>12.265</v>
       </c>
       <c r="R50" t="n">
-        <v>22.562</v>
+        <v>22.676</v>
       </c>
       <c r="S50" t="n">
-        <v>23.875</v>
+        <v>23.853</v>
       </c>
       <c r="T50" t="n">
-        <v>3212</v>
+        <v>3390</v>
       </c>
       <c r="U50" t="n">
-        <v>9.875</v>
+        <v>10.059</v>
       </c>
       <c r="V50" t="n">
-        <v>8.688000000000001</v>
+        <v>8.618</v>
       </c>
       <c r="W50" t="n">
-        <v>5.156</v>
+        <v>5.118</v>
       </c>
       <c r="X50" t="n">
-        <v>2.938</v>
+        <v>2.912</v>
       </c>
       <c r="Y50" t="n">
-        <v>30.531</v>
+        <v>30.294</v>
       </c>
       <c r="Z50" t="n">
-        <v>39.719</v>
+        <v>39.353</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="AB50" t="n">
-        <v>5.656</v>
+        <v>5.647</v>
       </c>
       <c r="AC50" t="n">
-        <v>12.125</v>
+        <v>12.265</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.466</v>
+        <v>0.46</v>
       </c>
       <c r="AE50" t="n">
-        <v>3.031</v>
+        <v>3.029</v>
       </c>
       <c r="AF50" t="n">
-        <v>8.093999999999999</v>
+        <v>8.324</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.375</v>
+        <v>0.364</v>
       </c>
       <c r="AH50" t="n">
-        <v>3.094</v>
+        <v>3</v>
       </c>
       <c r="AI50" t="n">
-        <v>7.156</v>
+        <v>6.912</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.432</v>
+        <v>0.434</v>
       </c>
       <c r="AK50" t="n">
-        <v>6.312</v>
+        <v>6.588</v>
       </c>
       <c r="AL50" t="n">
-        <v>18.875</v>
+        <v>18.971</v>
       </c>
       <c r="AM50" t="n">
-        <v>0.334</v>
+        <v>0.347</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>201:33</t>
+          <t>201:28</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>84.636</v>
+        <v>84.435</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.556</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.607</v>
+        <v>0.608</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.027</v>
+        <v>1.03</v>
       </c>
       <c r="AS50" t="n">
-        <v>0.154</v>
+        <v>0.153</v>
       </c>
       <c r="AT50" t="n">
-        <v>0.327</v>
+        <v>0.328</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.303</v>
+        <v>1.291</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.192</v>
+        <v>0.191</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.047</v>
+        <v>0.046</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.159</v>
+        <v>0.157</v>
       </c>
       <c r="AY50" t="n">
         <v>0</v>
